--- a/purgrace/seo/PurGrace-SEO.xlsx
+++ b/purgrace/seo/PurGrace-SEO.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Produtos'!$A$1:$X$163</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coleções'!$A$1:$N$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Problemas'!$A$1:$D$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coleções'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Problemas'!$A$1:$D$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Anéis'!$A$1:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,7 +842,7 @@
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista; corrigiu 'Romanel' para 'Rommanel'</t>
+          <t>corrigiu 'Romanel' para 'Rommanel'</t>
         </is>
       </c>
       <c r="W2" s="6" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
       <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista; corrigiu 'Romanel' para 'Rommanel'</t>
+          <t>corrigiu 'Romanel' para 'Rommanel'</t>
         </is>
       </c>
       <c r="W10" s="6" t="inlineStr"/>
@@ -1684,11 +1684,7 @@
       </c>
       <c r="T11" s="4" t="inlineStr"/>
       <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>tirou 'Waterproof' da lista; tirou 'water resistant'; trocou o cuidado 'Although water resistant' pela orientação da Rommanel</t>
-        </is>
-      </c>
+      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="6" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
     </row>
@@ -1966,7 +1962,7 @@
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr"/>
@@ -2062,7 +2058,7 @@
       <c r="U15" s="4" t="inlineStr"/>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr"/>
@@ -2158,7 +2154,7 @@
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr"/>
@@ -2346,7 +2342,7 @@
       <c r="U18" s="4" t="inlineStr"/>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr"/>
@@ -2538,7 +2534,7 @@
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr"/>
@@ -2634,7 +2630,7 @@
       <c r="U21" s="4" t="inlineStr"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista; tirou 'water resistant'; corrigiu 'Romanel' para 'Rommanel'</t>
+          <t>corrigiu 'Romanel' para 'Rommanel'</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr"/>
@@ -3474,7 +3470,7 @@
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>tirou '✨ Waterproof'</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr"/>
@@ -3574,7 +3570,7 @@
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr"/>
@@ -3670,7 +3666,7 @@
       <c r="U32" s="4" t="inlineStr"/>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista; corrigiu 'CChain'</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'; corrigiu 'CChain'</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr"/>
@@ -4226,7 +4222,7 @@
       <c r="U38" s="4" t="inlineStr"/>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr"/>
@@ -4322,7 +4318,7 @@
       <c r="U39" s="4" t="inlineStr"/>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
@@ -4422,7 +4418,7 @@
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr"/>
@@ -4610,7 +4606,7 @@
       <c r="U42" s="4" t="inlineStr"/>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr"/>
@@ -4794,7 +4790,7 @@
       <c r="U44" s="4" t="inlineStr"/>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr"/>
@@ -4890,7 +4886,7 @@
       <c r="U45" s="4" t="inlineStr"/>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W45" s="6" t="inlineStr"/>
@@ -4986,7 +4982,7 @@
       <c r="U46" s="4" t="inlineStr"/>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W46" s="6" t="inlineStr"/>
@@ -5086,7 +5082,7 @@
       <c r="U47" s="4" t="inlineStr"/>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W47" s="6" t="inlineStr"/>
@@ -5186,7 +5182,7 @@
       <c r="U48" s="4" t="inlineStr"/>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W48" s="6" t="inlineStr"/>
@@ -6506,7 +6502,7 @@
       <c r="U62" s="4" t="inlineStr"/>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Waterproof' da lista</t>
+          <t>trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W62" s="6" t="inlineStr"/>
@@ -7914,7 +7910,7 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>18k gold plated, kids, resin</t>
+          <t>18k gold plated, kids, disney, resin</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -16356,7 +16352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17063,7 +17059,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>diz que a peça é à prova d'água</t>
+          <t>diz 'waterproof'; troque por 'water-resistant'</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -17181,11 +17177,7 @@
           <t>Celebrate her with something she’ll wear every day 🤍 Our Mother’s Day selection was created for meaningful gifting — timeless, elegant pieces she’ll love beyond the moment. 18k gold plated jewellery Water-resistant &amp; made for everyday wear Make this Mother’s Day unforgettable!</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>diz que a peça é à prova d'água</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Gifts she'll wear every day: boy and girl pendants, hearts and family bracelets, plated in 18K gold by Rommanel.</t>
@@ -17247,7 +17239,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>diz que a peça é à prova d'água; anuncia 30% OFF</t>
+          <t>diz 'waterproof'; troque por 'water-resistant'; anuncia 30% OFF</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -17283,8 +17275,164 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>gifts-for-her</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Gifts for Her</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Hearts, butterflies and ready-to-give sets for your girlfriend, your wife or your best friend.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Gifts for Her – Hearts, Butterflies &amp; Sets | Rommanel</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Rommanel gifts for her: heart and butterfly jewellery and ready-to-give sets plated in 18K gold, for a girlfriend, wife or friend. Shipped from Perth.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Coleção nova para o guia de presentes. Crie como automática, com qualquer condição: Tag é igual a love, Tag é igual a butterfly, Tag é igual a gift set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>gifts-for-him</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Gifts for Him</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Chains, crosses and scapulars for your boyfriend, your husband or your dad.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Gifts for Him – Chains, Crosses &amp; Scapulars | Rommanel</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>18K gold-plated chains, crosses and scapulars by Rommanel for your boyfriend, husband or dad. Nickel-free, shipped from Perth Australia-wide.</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Coleção nova para o guia de presentes. Crie como automática, com qualquer condição: Tag é igual a men, Tag é igual a unisex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>disney</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Pieces from the Rommanel Disney line, plated in 18K gold.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Disney Jewellery – 18K Gold Plated | Rommanel Australia</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Pieces from the Rommanel Disney line plated in 18K gold, like Cinderella and Lotso: a magical gift for kids and fans. Shipped from Perth.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Coleção nova para o guia de presentes. Crie como automática: Tag é igual a disney. Peça nova da linha Disney entra sozinha quando tiver a tag disney.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -17300,6 +17448,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17311,7 +17462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18324,11 +18475,11 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Saint Benedict Medal Pendant</t>
+          <t>18K Gold-Plated Holy Spirit Dove Earrings</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -18338,17 +18489,17 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Textured Cross Pendant</t>
+          <t>18K Gold-Plated Triple Hoop Earrings</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -18358,17 +18509,17 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Men's 18K Gold-Plated Chain Necklace, 60 cm</t>
+          <t>18K Gold-Plated Four-Leaf Clover Earrings</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -18378,17 +18529,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Holy Spirit Dove Earrings</t>
+          <t>18K Gold-Plated Hoop Earrings with Pear Cubic Zirconia Drops</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -18398,17 +18549,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Triple Hoop Earrings</t>
+          <t>18K Gold-Plated Flower Stud Earring Set</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -18418,17 +18569,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Four-Leaf Clover Earrings</t>
+          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -18438,17 +18589,17 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Hoop Earrings with Pear Cubic Zirconia Drops</t>
+          <t>18K Gold-Plated Bezel Crystal Stud Earrings, 4 mm</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -18458,17 +18609,17 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Flower Stud Earring Set</t>
+          <t>18K Gold-Plated Cable Chain Necklace, 50 cm</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -18478,17 +18629,17 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Men's 18K Gold-Plated Cross Scapular Necklace, 68 cm</t>
+          <t>18K Gold-Plated Cable Chain Necklace, 45 cm</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -18498,17 +18649,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
+          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -18518,17 +18669,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Bezel Crystal Stud Earrings, 4 mm</t>
+          <t>18K Gold-Plated Crystal Solitaire Stud Earrings</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -18538,17 +18689,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Cable Chain Necklace, 50 cm</t>
+          <t>Children's 18K Gold-Plated Ball Drop Earrings</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -18558,17 +18709,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Cable Chain Necklace, 45 cm</t>
+          <t>18K Gold-Plated Textured Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -18578,17 +18729,17 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
+          <t>Children's 18K Gold-Plated Bow Stud Earrings</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -18598,17 +18749,17 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Crystal Solitaire Stud Earrings</t>
+          <t>18K Gold-Plated Wide Huggie Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -18618,17 +18769,17 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Children's 18K Gold-Plated Ball Drop Earrings</t>
+          <t>18K Gold-Plated Crystal Ear Climber Earrings</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -18638,17 +18789,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Textured Hoop Earrings, 1.3 cm</t>
+          <t>18K Gold-Plated Oval Hoop Earrings, 1.8 cm</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -18658,17 +18809,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Children's 18K Gold-Plated Bow Stud Earrings</t>
+          <t>18K Gold-Plated Lock Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -18678,77 +18829,73 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
-        <v>44</v>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Wide Huggie Hoop Earrings, 1.3 cm</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
+          <t>Todas as fotos</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>Nenhuma das 436 fotos tem texto alternativo. O tema novo usa o título limpo como texto alternativo enquanto você não escreve um, mas o ideal é descrever cada foto (ex.: 'brinco de borboleta na orelha da modelo').</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>45</v>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Crystal Ear Climber Earrings</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
+          <t>Tipos de produto</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>Hoje há 9 grafias diferentes para as mesmas coisas (EARRINGS, EARRING, Brinco, CHEKER...) e 33 produtos sem tipo. A importação 1 deixa só 7: Earrings, Necklaces, Pendants, Rings, Bracelets, Anklets, Jewellery Sets.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
-        <v>46</v>
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Oval Hoop Earrings, 1.8 cm</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
+          <t>Coleções incompletas</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>63 produtos não estão na coleção da categoria deles (ex.: 25 brincos fora de 'Earrings'). Com os tipos padronizados, dá para transformar as coleções em automáticas (veja o guia).</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>60</v>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Lock Chain Necklace, 42 cm</t>
+          <t>Coleção 18K Gold Plated</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -18758,7 +18905,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz que a peça é à prova d'água (waterproof/water resistant). A Rommanel orienta tirar as joias para mar, piscina e banho: a importação 2 tira essa frase.</t>
+          <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
@@ -18770,13 +18917,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Todas as fotos</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr"/>
+          <t>Coleção All Jewellery</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Nenhuma das 436 fotos tem texto alternativo. O tema novo usa o título limpo como texto alternativo enquanto você não escreve um, mas o ideal é descrever cada foto (ex.: 'brinco de borboleta na orelha da modelo').</t>
+          <t>O texto diz 'waterproof' (troque por 'water-resistant'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
@@ -18788,13 +18939,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Tipos de produto</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
+          <t>Coleção EOFY Gold</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Hoje há 9 grafias diferentes para as mesmas coisas (EARRINGS, EARRING, Brinco, CHEKER...) e 33 produtos sem tipo. A importação 1 deixa só 7: Earrings, Necklaces, Pendants, Rings, Bracelets, Anklets, Jewellery Sets.</t>
+          <t>O texto diz 'waterproof' (troque por 'water-resistant'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
@@ -18806,128 +18961,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Coleções incompletas</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr"/>
+          <t>Página About us</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>63 produtos não estão na coleção da categoria deles (ex.: 25 brincos fora de 'Earrings'). Com os tipos padronizados, dá para transformar as coleções em automáticas (veja o guia).</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Coleção 18K Gold Plated</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Coleção All Jewellery</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>O texto diz que as peças são à prova d'água (waterproof/water-resistant). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Coleção EOFY Gold</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>O texto diz que as peças são à prova d'água (waterproof/water-resistant). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Coleção Mother’s day</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>O texto diz que as peças são à prova d'água (waterproof/water-resistant). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Página About us</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
           <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Loja virtual › Páginas, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D80"/>
+  <autoFilter ref="A1:D75"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -18996,15 +19045,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/purgrace/seo/PurGrace-SEO.xlsx
+++ b/purgrace/seo/PurGrace-SEO.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Anéis" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Produtos'!$A$1:$X$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Produtos'!$A$1:$Y$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coleções'!$A$1:$N$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Problemas'!$A$1:$D$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Problemas'!$A$1:$D$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Anéis'!$A$1:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -558,7 +558,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3. Importe nesta ordem, esperando o e-mail de confirmação de cada um: shopify-import-0-teste-2-produtos.csv (2 produtos; confira na loja), shopify-import-1-titulos-tipos-tags.csv (162), shopify-import-2-descricoes.csv (25) e, se quiser, shopify-import-3-seo-onde-falta.csv (só os produtos sem título e descrição para o Google hoje).</t>
+          <t>3. Importe nesta ordem, esperando o e-mail de confirmação de cada um: shopify-import-0-teste-2-produtos.csv (2 produtos; confira na loja), shopify-import-1-titulos-tipos-tags.csv (162), shopify-import-2-descricoes.csv (162 descrições novas; leia algumas na coluna 'Descrição nova' antes) e, se quiser, shopify-import-3-seo-onde-falta.csv (só os produtos sem título e descrição para o Google hoje).</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X163"/>
+  <dimension ref="A1:Y163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -626,8 +626,9 @@
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="70" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="50" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -743,10 +744,15 @@
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
+          <t>Descrição nova (importação 2)</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>URL nova sugerida (mudar à mão, com redirecionamento)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Atenção</t>
         </is>
@@ -842,11 +848,22 @@
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>corrigiu 'Romanel' para 'Rommanel'</t>
-        </is>
-      </c>
-      <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>Saint Benedict medal pendant by Rommanel, petite and plated in 18K gold, a traditional symbol of faith and protection to wear every day. A meaningful gift for a baptism or a godchild.
+• Material: 18K gold plated, with three layers of gold
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="inlineStr"/>
+      <c r="Y2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -936,9 +953,26 @@
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
       <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="7" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>A little girl pendant set with sparkling cubic zirconia, to keep a daughter close to your heart. A sweet gift for a new mum or for Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm x 0.9 cm
+• Stones: 18 cubic zirconia, 1 mm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje começa com "8K ": falta o 1 de 18K.</t>
         </is>
@@ -1036,9 +1070,25 @@
       </c>
       <c r="T4" s="4" t="inlineStr"/>
       <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="6" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>Romantic heart link necklace plated in 18K gold, with a 42 cm chain of faceted heart-shaped links for a pretty everyday look. A lovely gift for Valentine's Day or an anniversary.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Faceted heart-shaped link chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1128,9 +1178,25 @@
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
       <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="6" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>Two-tone girl pendant, plated in 18K gold and rhodium, a quiet tribute to a daughter or granddaughter that you can wear every day. A thoughtful gift for a proud mum or nan.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Two-tone gold and rhodium plating
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1220,9 +1286,25 @@
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="6" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>Butterfly earrings plated in 18K gold, one side of each butterfly set with navette-cut cubic zirconia for a flash of sparkle. Pretty for every day and dressy enough for special occasions.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm x 1.3 cm
+• Stones: Two 4 x 8 mm and two 3 x 6 mm navette cubic zirconia per pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1312,9 +1394,24 @@
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="6" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>Everyday fine chain necklace plated in 18K gold, 50 cm long, to wear on its own or layered with shorter chains. An easy gift for a friend, a sister or yourself.
+• Material: 18K gold plated, with three layers of gold
+• Length: 50 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1396,9 +1493,25 @@
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
       <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>Matching butterfly jewellery set with a 3D open butterfly necklace and a pair of butterfly earrings, all plated in 18K gold. Wear them together for a coordinated look or style each piece on its own.
+• Material: 18K gold plated, with three layers of gold
+• Includes a butterfly necklace and a pair of matching butterfly earrings
+• 3D butterfly design
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="7" t="inlineStr">
         <is>
           <t>Conjunto montado pela loja: o número no título (003) não é código Rommanel, então fica sem SKU e sem MPN.</t>
         </is>
@@ -1496,9 +1609,23 @@
       </c>
       <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>Pretty necklace with an open butterfly pendant, plated in 18K gold, that works on its own or layered with longer chains. A charming birthday gift for a daughter, sister or friend.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1590,11 +1717,23 @@
       <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>corrigiu 'Romanel' para 'Rommanel'</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>Unisex textured cross pendant plated in 18K gold, a classic piece of Christian jewellery for men and women alike. Pair it with a 60 cm chain or one you already own; a fitting gift for Easter, a Confirmation or a godson.
+• Material: 18K gold plated, with three layers of gold
+• Unisex design
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1684,9 +1823,24 @@
       </c>
       <c r="T11" s="4" t="inlineStr"/>
       <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="6" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>Men's gold chain by Rommanel, 60 cm long with an 18K gold-plated finish, classic enough to wear alone or layered with other pieces. A good Father's Day or birthday gift for a husband, boyfriend or dad.
+• Material: 18K gold plated, with three layers of gold
+• Length: 60 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1772,9 +1926,26 @@
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="4" t="inlineStr"/>
       <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="6" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
+          <t>Dragonfly anklet plated in 18K gold, with a smooth dragonfly charm on a laminated-link chain, 25 cm long and adjustable to 23 cm. A pretty finishing touch for sandals and summer dresses, and a fun gift for a nature lover.
+• Material: 18K gold plated, with three layers of gold
+• Length: 25 cm, adjustable to 23 cm
+• Laminated-link chain
+• Smooth dragonfly charm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1864,9 +2035,24 @@
       </c>
       <c r="T13" s="4" t="inlineStr"/>
       <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="6" t="inlineStr"/>
-      <c r="X13" s="7" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>Baroque pearl pendant necklace by Rommanel, plated in 18K gold, where the pearl's irregular shape gives a modern twist to a classic look. A graceful gift for a bride, a bridesmaid or a June birthday.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Baroque pearl
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="7" t="inlineStr">
         <is>
           <t>Descrição vazia: escreva comprimento e medidas da pérola.</t>
         </is>
@@ -1962,11 +2148,22 @@
       <c r="U14" s="4" t="inlineStr"/>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>Small Holy Spirit dove earrings, 0.5 cm x 0.7 cm and plated in 18K gold, for a discreet sign of faith you can wear every day. A special gift for a Confirmation.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.5 cm x 0.7 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2058,11 +2255,21 @@
       <c r="U15" s="4" t="inlineStr"/>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>Triple hoop earrings with an 18K gold-plated finish, a fresh take on classic gold hoops that goes from casual days to evenings out. A fun birthday gift for a friend who loves hoops.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2154,11 +2361,22 @@
       <c r="U16" s="4" t="inlineStr"/>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W16" s="6" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>Four-leaf clover earrings in 18K gold plating, 1 cm across: a little symbol of good luck to wear every day. A thoughtful gift for a new job, exam season or a friend's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1 cm x 1 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2248,9 +2466,25 @@
       </c>
       <c r="T17" s="4" t="inlineStr"/>
       <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="6" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W17" s="6" t="inlineStr">
+        <is>
+          <t>Clip-on ear cuff in 18K gold plating with an open design, an easy way to dress up the ear without a piercing. Wear it on its own or alongside your favourite studs and hoops.
+• Material: 18K gold plated, with three layers of gold
+• Clip-on, no piercing needed
+• Open design
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2342,11 +2576,23 @@
       <c r="U18" s="4" t="inlineStr"/>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>Pear-shaped cubic zirconia drops hang from these 18K gold-plated hoop earrings by Rommanel, adding sparkle to a classic shape. Dressy enough for weddings and dinners, simple enough for the office.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.2 cm x 0.4 cm
+• Stones: Two 4 x 6 mm pear-shaped cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2436,9 +2682,23 @@
       </c>
       <c r="T19" s="4" t="inlineStr"/>
       <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="6" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>Hoop earrings with cross drops, plated in 18K gold, pairing a classic hoop with a symbol of faith for everyday wear. A lovely gift for a goddaughter or a friend who shares your faith.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="7" t="inlineStr">
         <is>
           <t>Descrição vazia: escreva medidas e fecho.</t>
         </is>
@@ -2534,11 +2794,21 @@
       <c r="U20" s="4" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W20" s="6" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
+        <is>
+          <t>Flower stud earring set plated in 18K gold, with floral studs to mix and match from one day to the next. A pretty birthday or Mother's Day gift for anyone who loves flowers.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr"/>
+      <c r="Y20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2630,11 +2900,24 @@
       <c r="U21" s="4" t="inlineStr"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>corrigiu 'Romanel' para 'Rommanel'</t>
-        </is>
-      </c>
-      <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr"/>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="inlineStr">
+        <is>
+          <t>Catholic scapular necklace for men by Rommanel, with two cross pendants on a 68 cm lock-link chain plated in 18K gold. A meaningful gift for Father's Day, a Confirmation or a birthday.
+• Material: 18K gold plated, with three layers of gold
+• Length: 68 cm
+• Two cross pendants
+• Lock-link chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr"/>
+      <c r="Y21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2724,9 +3007,27 @@
       </c>
       <c r="T22" s="4" t="inlineStr"/>
       <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>Scapular necklace pairing Our Lady of Mount Carmel and the Sacred Heart of Jesus on two heart-shaped medals, with a 49 cm lock-link chain plated in 18K gold. A unisex piece for everyday devotion and a heartfelt Catholic gift.
+• Material: 18K gold plated, with three layers of gold
+• Length: 49 cm
+• Two heart-shaped medals: the Sacred Heart of Jesus and Our Lady of Mount Carmel
+• Lock-link chain
+• Unisex design
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr"/>
+      <c r="Y22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2820,9 +3121,26 @@
       </c>
       <c r="T23" s="4" t="inlineStr"/>
       <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="7" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>Delicate 42 cm necklace on a fine 0.2 mm lock chain, plated in 18K gold for a minimal everyday look. Lovely on its own or layered with longer chains and pendants.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Fine lock chain, 0.2 mm
+• Padlock clasp
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr"/>
+      <c r="Y23" s="7" t="inlineStr">
         <is>
           <t>Parece ser o mesmo colar do #109 (mesmo código-base 531638, mesma descrição). Mantenha um só e crie um redirecionamento do outro.</t>
         </is>
@@ -2916,9 +3234,25 @@
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="4" t="inlineStr"/>
       <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="7" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>Venetian chain necklace by Rommanel, plated in 18K gold: 42 cm of fine 0.9 mm Venetian chain with a clean, simple line. Wear it alone or as a neat base for layering.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Venetian chain, 0.9 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr"/>
+      <c r="Y24" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -3016,9 +3350,23 @@
       </c>
       <c r="T25" s="4" t="inlineStr"/>
       <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>Openwork butterfly stud earrings plated in 18K gold, airy and delicate for everyday wear. A gift for a daughter, niece or friend who loves butterflies.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr"/>
+      <c r="Y25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -3108,9 +3456,25 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
       <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>Boy pendant with a two-tone finish of 18K gold and rhodium plating, for mums who like to keep a son close every day. A loving Mother's Day gift, or a keepsake for a mum welcoming a baby boy.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Two-tone gold and rhodium plating
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr"/>
+      <c r="Y26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -3200,9 +3564,26 @@
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="4" t="inlineStr"/>
       <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>Half hoop earring set with two pairs of smooth gold-plated half-hoops in different sizes, from the licensed Ana Hickmann collection by Rommanel. Wear one pair alone or both together if you have a second piercing.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.1 cm x 0.9 cm
+• Two pairs of smooth half-hoops in different sizes
+• From the licensed Ana Hickmann collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr"/>
+      <c r="Y27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -3292,9 +3673,24 @@
       <c r="S28" s="4" t="inlineStr"/>
       <c r="T28" s="4" t="inlineStr"/>
       <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>Dainty openwork butterfly studs in 18K gold plating, 0.9 cm x 1.2 cm, for a small flutter of gold on the ear. A pretty choice for everyday wear or a best friend's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.9 cm x 1.2 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X28" s="6" t="inlineStr"/>
+      <c r="Y28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -3384,9 +3780,25 @@
       </c>
       <c r="T29" s="4" t="inlineStr"/>
       <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
+        <is>
+          <t>Nossa Senhora Aparecida pendant by Rommanel, plated in 18K gold with blue cubic zirconia, for devotees of Our Lady of Aparecida, patroness of Brazil. A heartfelt baptism gift, and a piece of home for Brazilians living in Australia.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Blue cubic zirconia
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -3404,7 +3816,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
+          <t>18K Gold-Plated Mini Butterfly Pendant and Earrings Set</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -3436,11 +3848,11 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Mini Butterfly Necklace and Earrings Set – 18K Gold Plated</t>
+          <t>Mini Butterfly Pendant and Earrings Set – 18K Gold Plated</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -3449,11 +3861,11 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Mini butterfly necklace and earrings set by Rommanel, plated in 18K gold. Nickel-free and hypoallergenic. Shipped Australia-wide from Perth.</t>
+          <t>Mini butterfly pendant and earrings set by Rommanel, plated in 18K gold. Nickel-free and hypoallergenic. Shipped Australia-wide from Perth.</t>
         </is>
       </c>
       <c r="P30" s="4" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
@@ -3462,7 +3874,7 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
+          <t>18K Gold-Plated Mini Butterfly Pendant and Earrings Set</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr"/>
@@ -3470,11 +3882,23 @@
       <c r="U30" s="4" t="inlineStr"/>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="7" t="inlineStr">
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W30" s="6" t="inlineStr">
+        <is>
+          <t>Mini butterfly jewellery set with an 18K gold-plated butterfly pendant and a pair of butterfly earrings, chosen to be worn together. A pretty pairing for a birthday, an anniversary or Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Includes a butterfly pendant and a pair of butterfly earrings
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X30" s="6" t="inlineStr"/>
+      <c r="Y30" s="7" t="inlineStr">
         <is>
           <t>Conjunto montado pela loja: o número no título (0000002) não é código Rommanel, então fica sem SKU e sem MPN.</t>
         </is>
@@ -3570,11 +3994,23 @@
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>Bezel-set crystal stud earrings plated in 18K gold, a classic 4 mm solitaire style with one crystal on each ear. Everyday sparkle, and a simple gift for bridesmaids or a friend's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 4 mm diameter
+• Stones: Two 4 mm crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr"/>
+      <c r="Y31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -3666,11 +4102,23 @@
       <c r="U32" s="4" t="inlineStr"/>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'; corrigiu 'CChain'</t>
-        </is>
-      </c>
-      <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'; corrigiu 'CChain'</t>
+        </is>
+      </c>
+      <c r="W32" s="6" t="inlineStr">
+        <is>
+          <t>Classic cable chain necklace plated in 18K gold, 50 cm long, with a simple linked design for everyday outfits. Wear it alone or layer it with shorter chains for a stacked look.
+• Material: 18K gold plated, with three layers of gold
+• Length: 50 cm
+• Cable link chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X32" s="6" t="inlineStr"/>
+      <c r="Y32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -3760,9 +4208,26 @@
       </c>
       <c r="T33" s="4" t="inlineStr"/>
       <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
+        <is>
+          <t>Double-sided pet mum medal pendant plated in 18K gold, with an inscription on one side and a paw print on the other. A sweet gift for a dog or cat lover, and a fun Mother's Day surprise from the fur babies.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2 cm x 1.1 cm
+• Double-sided: 'Pet Mom' inscribed on one side, a paw print on the other
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr"/>
+      <c r="Y33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -3852,9 +4317,26 @@
       </c>
       <c r="T34" s="4" t="inlineStr"/>
       <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W34" s="6" t="inlineStr">
+        <is>
+          <t>Heart-shaped Holy Spirit pendant plated in 18K gold, 1.7 cm x 1.3 cm, bringing faith and love together in one piece. A meaningful gift from a godparent or Confirmation sponsor.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.7 cm x 1.3 cm
+• Holy Spirit at the centre of the heart
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X34" s="6" t="inlineStr"/>
+      <c r="Y34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -3944,9 +4426,25 @@
       </c>
       <c r="T35" s="4" t="inlineStr"/>
       <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W35" s="6" t="inlineStr">
+        <is>
+          <t>Fé pendant, Portuguese for faith, plated in 18K gold and set with cubic zirconia. A sparkling everyday reminder of what you believe and a thoughtful gift for a Confirmation or baptism.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4036,9 +4534,25 @@
       </c>
       <c r="T36" s="4" t="inlineStr"/>
       <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W36" s="6" t="inlineStr">
+        <is>
+          <t>Blessed Sacrament pendant plated in 18K gold with a resin stone, a devotional piece celebrating the Eucharist. A meaningful gift for a First Holy Communion or for anyone devoted to Eucharistic adoration.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Resin stone
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X36" s="6" t="inlineStr"/>
+      <c r="Y36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4128,9 +4642,26 @@
       </c>
       <c r="T37" s="4" t="inlineStr"/>
       <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W37" s="6" t="inlineStr">
+        <is>
+          <t>Round Holy Spirit pendant plated in 18K gold and fully set with cubic zirconia, so the whole design sparkles. A lovely gift for Pentecost or a Confirmation, and an everyday sign of faith.
+• Material: 18K gold plated, with three layers of gold
+• Stones: 38 cubic zirconia, 1 mm and 1.5 mm
+• Holy Spirit motif at the centre
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4222,11 +4753,23 @@
       <c r="U38" s="4" t="inlineStr"/>
       <c r="V38" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W38" s="6" t="inlineStr">
+        <is>
+          <t>Medium-length cable chain necklace, 45 cm and plated in 18K gold, an easy everyday chain to wear alone or layer. A simple gift for a friend or a daughter.
+• Material: 18K gold plated, with three layers of gold
+• Length: 45 cm
+• Cable link chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X38" s="6" t="inlineStr"/>
+      <c r="Y38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4318,15 +4861,27 @@
       <c r="U39" s="4" t="inlineStr"/>
       <c r="V39" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
+          <t>Curb chain necklace in 18K gold plating, where smooth curb chain alternates with twisted curb chain along a 42 cm length. The mix of textures gives a simple gold chain a little extra interest, alone or layered.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Smooth curb chain alternating with twisted curb chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X39" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-curb-chain-necklace-42-cm-5306944200</t>
         </is>
       </c>
-      <c r="X39" s="4" t="inlineStr"/>
+      <c r="Y39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -4418,11 +4973,23 @@
       <c r="U40" s="4" t="inlineStr"/>
       <c r="V40" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W40" s="6" t="inlineStr">
+        <is>
+          <t>Solitaire stud earrings plated in 18K gold, each with a single 4 mm crystal for a classic point of light. Easy to pair with hoops or wear alone, and a lovely graduation or birthday gift.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.4 cm diameter
+• Stones: Two 4 mm crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X40" s="6" t="inlineStr"/>
+      <c r="Y40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4512,9 +5079,24 @@
       </c>
       <c r="T41" s="4" t="inlineStr"/>
       <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
+          <t>Kids' heart stud earrings plated in 18K gold with cubic zirconia, a sweet little pair made for children. A lovely gift for a birthday, a baptism or a flower girl.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X41" s="6" t="inlineStr"/>
+      <c r="Y41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -4606,11 +5188,22 @@
       <c r="U42" s="4" t="inlineStr"/>
       <c r="V42" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>Ball drop earrings for kids in 18K gold plating, a simple 1 cm design with a playful touch of shine. A cute Christmas stocking filler or birthday gift for a little one.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X42" s="6" t="inlineStr"/>
+      <c r="Y42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4692,9 +5285,26 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="4" t="inlineStr"/>
       <c r="U43" s="4" t="inlineStr"/>
-      <c r="V43" s="4" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="7" t="inlineStr">
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>Matching gold-plated heart necklace and earrings set by Rommanel: a Singapore chain with a heart charm and a pair of open-heart earrings with cubic zirconia. A lovely gift for a birthday, an anniversary or Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Necklace: Singapore chain with a heart charm
+• Earrings: open-heart design
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X43" s="6" t="inlineStr"/>
+      <c r="Y43" s="7" t="inlineStr">
         <is>
           <t>Conjunto montado pela loja: o número no título (00012026) não é código Rommanel, então fica sem SKU e sem MPN.</t>
         </is>
@@ -4790,11 +5400,22 @@
       <c r="U44" s="4" t="inlineStr"/>
       <c r="V44" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W44" s="6" t="inlineStr">
+        <is>
+          <t>Textured gold-plated hoop earrings with raised detailing, measuring 1.3 cm. A small everyday pair that adds subtle interest to simple outfits, worn alone or with your favourite pieces.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X44" s="6" t="inlineStr"/>
+      <c r="Y44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -4886,11 +5507,21 @@
       <c r="U45" s="4" t="inlineStr"/>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
+          <t>Kids' bow stud earrings plated in 18K gold by Rommanel, a sweet design made for children. A pretty birthday gift, or a treat for a little one's first jewellery box.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X45" s="6" t="inlineStr"/>
+      <c r="Y45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -4982,11 +5613,22 @@
       <c r="U46" s="4" t="inlineStr"/>
       <c r="V46" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W46" s="6" t="inlineStr">
+        <is>
+          <t>Wide huggie hoop earrings in 18K gold plating, with a half-round profile and a size of 1.3 cm. Small but bold, they make a go-to pair for everyday wear.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X46" s="6" t="inlineStr"/>
+      <c r="Y46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5082,11 +5724,22 @@
       <c r="U47" s="4" t="inlineStr"/>
       <c r="V47" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W47" s="6" t="inlineStr">
+        <is>
+          <t>Crystal ear climber earrings plated in 18K gold, designed to rise up from the lobe along the ear. A modern, sparkly way to dress up a simple look or finish an ear stack.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X47" s="6" t="inlineStr"/>
+      <c r="Y47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5182,11 +5835,22 @@
       <c r="U48" s="4" t="inlineStr"/>
       <c r="V48" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W48" s="6" t="inlineStr">
+        <is>
+          <t>Oval hoop earrings in 18K gold plating, measuring 1.8 cm: a softer, elongated twist on the classic round hoop. Simple enough for every day and dressy enough for evenings out.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.8 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X48" s="6" t="inlineStr"/>
+      <c r="Y48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5276,9 +5940,25 @@
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="4" t="inlineStr"/>
       <c r="U49" s="4" t="inlineStr"/>
-      <c r="V49" s="4" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W49" s="6" t="inlineStr">
+        <is>
+          <t>Delicate gold-plated chain necklace made from fine hammered links, 42 cm long. Wear it on its own as a minimal everyday chain or layer it with other necklaces.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Hammered link chain, 0.4 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X49" s="6" t="inlineStr"/>
+      <c r="Y49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -5368,13 +6048,31 @@
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="4" t="inlineStr"/>
       <c r="U50" s="4" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
+          <t>Solitaire pendant necklace in 18K gold plating, with a single 4 mm cubic zirconia on a Venetian chain, 40 cm long. A classic piece from Rommanel's licensed Giovanna Antonelli collection for everyday wear and special occasions.
+• Material: 18K gold plated, with three layers of gold
+• Length: 40 cm
+• Stones: One 4 mm cubic zirconia
+• Venetian chain
+• From the licensed Giovanna Antonelli collection, 12th edition
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X50" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-solitaire-pendant-necklace-40-cm-53200506</t>
         </is>
       </c>
-      <c r="X50" s="4" t="inlineStr"/>
+      <c r="Y50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5468,9 +6166,25 @@
       </c>
       <c r="T51" s="4" t="inlineStr"/>
       <c r="U51" s="4" t="inlineStr"/>
-      <c r="V51" s="4" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="4" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W51" s="6" t="inlineStr">
+        <is>
+          <t>Puffed heart pendant in 18K gold plating, 1.2 cm x 1.3 cm: a small, rounded symbol of love to add to your favourite chain. A sweet gift for a partner, a daughter or a best friend.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.2 cm x 1.3 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X51" s="6" t="inlineStr"/>
+      <c r="Y51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -5560,13 +6274,28 @@
       <c r="S52" s="4" t="inlineStr"/>
       <c r="T52" s="4" t="inlineStr"/>
       <c r="U52" s="4" t="inlineStr"/>
-      <c r="V52" s="4" t="inlineStr"/>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
+          <t>Classic gold-plated hoop earrings in a simple round shape, 1.8 cm across: a small everyday pair that goes from work to weekends.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.8 cm diameter
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X52" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-classic-hoop-earrings-1-8-cm-52080700</t>
         </is>
       </c>
-      <c r="X52" s="4" t="inlineStr"/>
+      <c r="Y52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5656,9 +6385,24 @@
       <c r="S53" s="4" t="inlineStr"/>
       <c r="T53" s="4" t="inlineStr"/>
       <c r="U53" s="4" t="inlineStr"/>
-      <c r="V53" s="4" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="4" t="inlineStr"/>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W53" s="6" t="inlineStr">
+        <is>
+          <t>Smooth hoop earrings plated in 18K gold and measuring 1.6 cm, with a plain, clean surface that keeps the look simple. A small, versatile hoop to wear every day with anything in your wardrobe.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.6 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X53" s="6" t="inlineStr"/>
+      <c r="Y53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5748,9 +6492,24 @@
       <c r="S54" s="4" t="inlineStr"/>
       <c r="T54" s="4" t="inlineStr"/>
       <c r="U54" s="4" t="inlineStr"/>
-      <c r="V54" s="4" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="4" t="inlineStr"/>
+      <c r="V54" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W54" s="6" t="inlineStr">
+        <is>
+          <t>Butterfly stud earrings in a two-tone finish that combines 18K gold plating with rhodium plating, so they pair easily with both gold and silver-tone jewellery. A pretty everyday pair and a thoughtful gift for butterfly lovers.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Two-tone: 18K gold and rhodium plating
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X54" s="6" t="inlineStr"/>
+      <c r="Y54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5840,9 +6599,24 @@
       <c r="S55" s="4" t="inlineStr"/>
       <c r="T55" s="4" t="inlineStr"/>
       <c r="U55" s="4" t="inlineStr"/>
-      <c r="V55" s="4" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="4" t="inlineStr"/>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W55" s="6" t="inlineStr">
+        <is>
+          <t>Pearl and crystal stud earrings in 18K gold plating, where synthetic pearls meet a touch of crystal sparkle. A classic pair for special occasions, or for dressing up an everyday outfit.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Synthetic pearls and crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X55" s="6" t="inlineStr"/>
+      <c r="Y55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5932,9 +6706,28 @@
       <c r="S56" s="4" t="inlineStr"/>
       <c r="T56" s="4" t="inlineStr"/>
       <c r="U56" s="4" t="inlineStr"/>
-      <c r="V56" s="4" t="inlineStr"/>
-      <c r="W56" s="6" t="inlineStr"/>
-      <c r="X56" s="4" t="inlineStr"/>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W56" s="6" t="inlineStr">
+        <is>
+          <t>Mini butterfly stud earrings in 18K gold plating, set with cubic zirconia for a little sparkle. Dainty enough for every day, and a pretty gift for a daughter, niece or friend.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X56" s="6" t="inlineStr"/>
+      <c r="Y56" s="7" t="inlineStr">
+        <is>
+          <t>O título e a descrição para o Google de hoje falam de anel ('Butterfly Ring for Girls'), mas a peça é um par de brincos de borboleta. Corrija em Search engine listing: as importações não mexem nesses textos.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -6024,9 +6817,25 @@
       <c r="S57" s="4" t="inlineStr"/>
       <c r="T57" s="4" t="inlineStr"/>
       <c r="U57" s="4" t="inlineStr"/>
-      <c r="V57" s="4" t="inlineStr"/>
-      <c r="W57" s="6" t="inlineStr"/>
-      <c r="X57" s="4" t="inlineStr"/>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W57" s="6" t="inlineStr">
+        <is>
+          <t>Ear climber earrings plated in 18K gold and set with cubic zirconia in three sizes, measuring 2.1 cm x 1 cm. Worn alone or as part of an ear stack, they bring extra sparkle to a night out.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.1 cm x 1 cm
+• Stones: Two 2.5 mm, two 3 mm and two 4 mm cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X57" s="6" t="inlineStr"/>
+      <c r="Y57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -6116,13 +6925,29 @@
       <c r="S58" s="4" t="inlineStr"/>
       <c r="T58" s="4" t="inlineStr"/>
       <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
+          <t>Interlocking circle stud earrings in 18K gold plating, with circles in high and low relief for a sculptural look. Small at 0.8 cm x 0.7 cm, they suit everyday wear and make a thoughtful gift for a friend.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.8 cm x 0.7 cm
+• Sold as a pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X58" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-interlocking-circles-earrings-52431000</t>
         </is>
       </c>
-      <c r="X58" s="4" t="inlineStr"/>
+      <c r="Y58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -6212,9 +7037,26 @@
       <c r="S59" s="4" t="inlineStr"/>
       <c r="T59" s="4" t="inlineStr"/>
       <c r="U59" s="4" t="inlineStr"/>
-      <c r="V59" s="4" t="inlineStr"/>
-      <c r="W59" s="6" t="inlineStr"/>
-      <c r="X59" s="4" t="inlineStr"/>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W59" s="6" t="inlineStr">
+        <is>
+          <t>Elegant pearl drop earrings that pair a smooth 18K gold-plated base with 8 mm synthetic pearls, measuring 1.3 cm. A refined choice for workwear, weddings and evenings out.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm
+• Stones: Two 8 mm synthetic pearls
+• Sold as a pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X59" s="6" t="inlineStr"/>
+      <c r="Y59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -6308,9 +7150,25 @@
       </c>
       <c r="T60" s="4" t="inlineStr"/>
       <c r="U60" s="4" t="inlineStr"/>
-      <c r="V60" s="4" t="inlineStr"/>
-      <c r="W60" s="6" t="inlineStr"/>
-      <c r="X60" s="4" t="inlineStr"/>
+      <c r="V60" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W60" s="6" t="inlineStr">
+        <is>
+          <t>Satin-finish girl face pendant plated in 18K gold, with a smooth bow and measuring 1 cm. A small keepsake for a mum to wear for her daughter, and a lovely gift for Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X60" s="6" t="inlineStr"/>
+      <c r="Y60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -6404,9 +7262,25 @@
       </c>
       <c r="T61" s="4" t="inlineStr"/>
       <c r="U61" s="4" t="inlineStr"/>
-      <c r="V61" s="4" t="inlineStr"/>
-      <c r="W61" s="6" t="inlineStr"/>
-      <c r="X61" s="4" t="inlineStr"/>
+      <c r="V61" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W61" s="6" t="inlineStr">
+        <is>
+          <t>Little boy face pendant in 18K gold plating, with a satin finish and a plain cap, 1 cm in size. A sweet tribute for mums of boys and a thoughtful gift for a new mum.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X61" s="6" t="inlineStr"/>
+      <c r="Y61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -6502,11 +7376,23 @@
       <c r="U62" s="4" t="inlineStr"/>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>trocou 'Waterproof' por 'Water-resistant'</t>
-        </is>
-      </c>
-      <c r="W62" s="6" t="inlineStr"/>
-      <c r="X62" s="4" t="inlineStr"/>
+          <t>descrição nova; trocou 'Waterproof' por 'Water-resistant'</t>
+        </is>
+      </c>
+      <c r="W62" s="6" t="inlineStr">
+        <is>
+          <t>Fine 18K gold-plated lock chain necklace, 42 cm long, for a minimal touch of gold. Wear it solo every day or layer it with longer chains.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Lock chain, 0.35 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X62" s="6" t="inlineStr"/>
+      <c r="Y62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -6600,9 +7486,25 @@
       </c>
       <c r="T63" s="4" t="inlineStr"/>
       <c r="U63" s="4" t="inlineStr"/>
-      <c r="V63" s="4" t="inlineStr"/>
-      <c r="W63" s="6" t="inlineStr"/>
-      <c r="X63" s="4" t="inlineStr"/>
+      <c r="V63" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W63" s="6" t="inlineStr">
+        <is>
+          <t>Domed heart pendant with grooved detailing, plated in 18K gold and measuring 1.6 cm x 1.2 cm. A classic love token for an anniversary, worn on a chain of your choice.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.6 cm x 1.2 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X63" s="6" t="inlineStr"/>
+      <c r="Y63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -6696,9 +7598,25 @@
       </c>
       <c r="T64" s="4" t="inlineStr"/>
       <c r="U64" s="4" t="inlineStr"/>
-      <c r="V64" s="4" t="inlineStr"/>
-      <c r="W64" s="6" t="inlineStr"/>
-      <c r="X64" s="4" t="inlineStr"/>
+      <c r="V64" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W64" s="6" t="inlineStr">
+        <is>
+          <t>Openwork butterfly pendant plated in 18K gold, with cut-out wings and a size of 1.4 cm x 0.8 cm. Hang it on a fine chain for an airy everyday look, or wear it alongside your other pendants.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.4 cm x 0.8 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X64" s="6" t="inlineStr"/>
+      <c r="Y64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -6792,9 +7710,26 @@
       </c>
       <c r="T65" s="4" t="inlineStr"/>
       <c r="U65" s="4" t="inlineStr"/>
-      <c r="V65" s="4" t="inlineStr"/>
-      <c r="W65" s="6" t="inlineStr"/>
-      <c r="X65" s="4" t="inlineStr"/>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W65" s="6" t="inlineStr">
+        <is>
+          <t>Sparkling cross pendant studded with cubic zirconia and plated in 18K gold, 2.5 cm x 1.8 cm, for wearing your faith every day. A meaningful gift for a First Holy Communion, Confirmation or baptism.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.5 cm x 1.8 cm
+• Stones: 31 cubic zirconia, 1 mm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X65" s="6" t="inlineStr"/>
+      <c r="Y65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -6888,9 +7823,25 @@
       </c>
       <c r="T66" s="4" t="inlineStr"/>
       <c r="U66" s="4" t="inlineStr"/>
-      <c r="V66" s="4" t="inlineStr"/>
-      <c r="W66" s="6" t="inlineStr"/>
-      <c r="X66" s="4" t="inlineStr"/>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W66" s="6" t="inlineStr">
+        <is>
+          <t>Pendant of a little boy doing keepy-uppies with a soccer ball, plated in 18K gold and measuring 2.4 cm. A fun piece for a proud soccer mum, or a gift for a young fan of the game.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.4 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X66" s="6" t="inlineStr"/>
+      <c r="Y66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -6984,9 +7935,23 @@
       </c>
       <c r="T67" s="4" t="inlineStr"/>
       <c r="U67" s="4" t="inlineStr"/>
-      <c r="V67" s="4" t="inlineStr"/>
-      <c r="W67" s="6" t="inlineStr"/>
-      <c r="X67" s="4" t="inlineStr"/>
+      <c r="V67" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W67" s="6" t="inlineStr">
+        <is>
+          <t>Large openwork butterfly earrings plated in 18K gold, a bolder pair for days when you want your earrings to be noticed. They look pretty with summer dresses, weekend outfits and evenings out.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X67" s="6" t="inlineStr"/>
+      <c r="Y67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -7080,9 +8045,25 @@
       </c>
       <c r="T68" s="4" t="inlineStr"/>
       <c r="U68" s="4" t="inlineStr"/>
-      <c r="V68" s="4" t="inlineStr"/>
-      <c r="W68" s="6" t="inlineStr"/>
-      <c r="X68" s="4" t="inlineStr"/>
+      <c r="V68" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W68" s="6" t="inlineStr">
+        <is>
+          <t>Two little boys joined by a heart in the centre form this 18K gold-plated family pendant, measuring 2.3 cm x 2.6 cm. A heartfelt choice for a mum of two sons, for Mother's Day or her birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.3 cm x 2.6 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X68" s="6" t="inlineStr"/>
+      <c r="Y68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -7176,9 +8157,25 @@
       </c>
       <c r="T69" s="4" t="inlineStr"/>
       <c r="U69" s="4" t="inlineStr"/>
-      <c r="V69" s="4" t="inlineStr"/>
-      <c r="W69" s="6" t="inlineStr"/>
-      <c r="X69" s="4" t="inlineStr"/>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W69" s="6" t="inlineStr">
+        <is>
+          <t>Daughters, sisters or best friends: this 18K gold-plated pendant shows two girls joined by a heart in the centre, measuring 2.3 cm x 2.7 cm. A lovely gift for a mum of two girls or a special sister.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.3 cm x 2.7 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X69" s="6" t="inlineStr"/>
+      <c r="Y69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -7272,9 +8269,25 @@
       </c>
       <c r="T70" s="4" t="inlineStr"/>
       <c r="U70" s="4" t="inlineStr"/>
-      <c r="V70" s="4" t="inlineStr"/>
-      <c r="W70" s="6" t="inlineStr"/>
-      <c r="X70" s="4" t="inlineStr"/>
+      <c r="V70" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W70" s="6" t="inlineStr">
+        <is>
+          <t>Boy and girl pendant in 18K gold plating, showing the two children joined by a heart in the centre and measuring 2.3 cm x 2.7 cm. A charming way for a mum of a son and a daughter to keep both close.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.3 cm x 2.7 cm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X70" s="6" t="inlineStr"/>
+      <c r="Y70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -7368,9 +8381,24 @@
       </c>
       <c r="T71" s="4" t="inlineStr"/>
       <c r="U71" s="4" t="inlineStr"/>
-      <c r="V71" s="4" t="inlineStr"/>
-      <c r="W71" s="6" t="inlineStr"/>
-      <c r="X71" s="4" t="inlineStr"/>
+      <c r="V71" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W71" s="6" t="inlineStr">
+        <is>
+          <t>Heart drop hoop earrings in 18K gold plating: small 1.1 cm hoops that each carry a domed heart. A romantic pair for Valentine's Day, an anniversary or a daughter's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2.3 cm x 0.7 cm, hoop 1.1 cm diameter
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X71" s="6" t="inlineStr"/>
+      <c r="Y71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -7464,9 +8492,24 @@
       </c>
       <c r="T72" s="4" t="inlineStr"/>
       <c r="U72" s="4" t="inlineStr"/>
-      <c r="V72" s="4" t="inlineStr"/>
-      <c r="W72" s="6" t="inlineStr"/>
-      <c r="X72" s="7" t="inlineStr">
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W72" s="6" t="inlineStr">
+        <is>
+          <t>Statement maxi ring in 18K gold plating, made of five intertwined wire strands with a 5 mm sphere at the centre. A bold, sculptural piece to wear on its own or as the focus of a ring stack.
+• Material: 18K gold plated, with three layers of gold
+• Five intertwined strands with a 5 mm sphere in the centre
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X72" s="6" t="inlineStr"/>
+      <c r="Y72" s="7" t="inlineStr">
         <is>
           <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
@@ -7564,9 +8607,25 @@
       </c>
       <c r="T73" s="4" t="inlineStr"/>
       <c r="U73" s="4" t="inlineStr"/>
-      <c r="V73" s="4" t="inlineStr"/>
-      <c r="W73" s="6" t="inlineStr"/>
-      <c r="X73" s="7" t="inlineStr">
+      <c r="V73" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W73" s="6" t="inlineStr">
+        <is>
+          <t>Triple band maxi ring plated in 18K gold, with an openwork design and three 4 mm cubic zirconia. Bold enough to wear on its own, it brings sparkle to evenings out and special occasions.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Three 4 mm cubic zirconia
+• Triple openwork band
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X73" s="6" t="inlineStr"/>
+      <c r="Y73" s="7" t="inlineStr">
         <is>
           <t>Anel sem opção de tamanho e com código curto (513639), sem o aro: veja o aro na etiqueta da peça e informe no anúncio.</t>
         </is>
@@ -7664,9 +8723,24 @@
       </c>
       <c r="T74" s="4" t="inlineStr"/>
       <c r="U74" s="4" t="inlineStr"/>
-      <c r="V74" s="4" t="inlineStr"/>
-      <c r="W74" s="6" t="inlineStr"/>
-      <c r="X74" s="4" t="inlineStr"/>
+      <c r="V74" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W74" s="6" t="inlineStr">
+        <is>
+          <t>Tiny openwork butterfly stud earrings in 18K gold plating, just 0.7 cm x 0.9 cm. A delicate everyday pair that also looks cute in a second piercing.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.7 cm x 0.9 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X74" s="6" t="inlineStr"/>
+      <c r="Y74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -7760,9 +8834,26 @@
       </c>
       <c r="T75" s="4" t="inlineStr"/>
       <c r="U75" s="4" t="inlineStr"/>
-      <c r="V75" s="4" t="inlineStr"/>
-      <c r="W75" s="6" t="inlineStr"/>
-      <c r="X75" s="7" t="inlineStr">
+      <c r="V75" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
+          <t>Small 18K gold-plated hoop earrings, 1.1 cm in diameter, finished with 5 mm cubic zirconia drops. A pretty, sparkly pair that works from day to evening.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2 cm x 0.6 cm, hoop 1.1 cm diameter
+• Stones: Two 5 mm cubic zirconia
+• Sold as a pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X75" s="6" t="inlineStr"/>
+      <c r="Y75" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -7860,9 +8951,23 @@
       </c>
       <c r="T76" s="4" t="inlineStr"/>
       <c r="U76" s="4" t="inlineStr"/>
-      <c r="V76" s="4" t="inlineStr"/>
-      <c r="W76" s="6" t="inlineStr"/>
-      <c r="X76" s="4" t="inlineStr"/>
+      <c r="V76" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W76" s="6" t="inlineStr">
+        <is>
+          <t>Beaded heart stud earrings plated in 18K gold, a sweet and romantic everyday pair. A lovely birthday gift for a best friend, a sister or someone you love.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X76" s="6" t="inlineStr"/>
+      <c r="Y76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -7956,9 +9061,24 @@
       </c>
       <c r="T77" s="4" t="inlineStr"/>
       <c r="U77" s="4" t="inlineStr"/>
-      <c r="V77" s="4" t="inlineStr"/>
-      <c r="W77" s="6" t="inlineStr"/>
-      <c r="X77" s="4" t="inlineStr"/>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
+          <t>Playful kids' Lotso bracelet plated in 18K gold, featuring the Disney and Pixar bear alongside a strawberry, with resin detail. A fun birthday gift for a young Toy Story fan.
+• Material: 18K gold plated, with three layers of gold
+• Lotso and strawberry design with resin detail
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X77" s="6" t="inlineStr"/>
+      <c r="Y77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -8052,9 +9172,26 @@
       </c>
       <c r="T78" s="4" t="inlineStr"/>
       <c r="U78" s="4" t="inlineStr"/>
-      <c r="V78" s="4" t="inlineStr"/>
-      <c r="W78" s="6" t="inlineStr"/>
-      <c r="X78" s="4" t="inlineStr"/>
+      <c r="V78" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W78" s="6" t="inlineStr">
+        <is>
+          <t>Gold-plated boy on a swing pendant, paired with a 4 mm round white cubic zirconia and measuring 3.3 cm. A tender piece for the mum of a little boy, to celebrate his arrival or her first Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 3.3 cm
+• Stones: One 4 mm round white cubic zirconia
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X78" s="6" t="inlineStr"/>
+      <c r="Y78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -8148,9 +9285,23 @@
       </c>
       <c r="T79" s="4" t="inlineStr"/>
       <c r="U79" s="4" t="inlineStr"/>
-      <c r="V79" s="4" t="inlineStr"/>
-      <c r="W79" s="6" t="inlineStr"/>
-      <c r="X79" s="4" t="inlineStr"/>
+      <c r="V79" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
+          <t>Starfish stud earrings plated in 18K gold, a beachy pair inspired by the sea. A cheerful pick for beach days and summer holidays, and a fun gift for ocean lovers.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X79" s="6" t="inlineStr"/>
+      <c r="Y79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -8244,9 +9395,23 @@
       </c>
       <c r="T80" s="4" t="inlineStr"/>
       <c r="U80" s="4" t="inlineStr"/>
-      <c r="V80" s="4" t="inlineStr"/>
-      <c r="W80" s="6" t="inlineStr"/>
-      <c r="X80" s="7" t="inlineStr">
+      <c r="V80" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W80" s="6" t="inlineStr">
+        <is>
+          <t>Skinny infinity ring plated in 18K gold, a slim stacking band featuring the infinity symbol as a quiet sign of lasting love or friendship. A thoughtful gift for a best friend, a sister or a partner.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X80" s="6" t="inlineStr"/>
+      <c r="Y80" s="7" t="inlineStr">
         <is>
           <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
@@ -8344,9 +9509,25 @@
       </c>
       <c r="T81" s="4" t="inlineStr"/>
       <c r="U81" s="4" t="inlineStr"/>
-      <c r="V81" s="4" t="inlineStr"/>
-      <c r="W81" s="6" t="inlineStr"/>
-      <c r="X81" s="7" t="inlineStr">
+      <c r="V81" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W81" s="6" t="inlineStr">
+        <is>
+          <t>Double band ring in 18K gold plating that pairs a row of 3 mm spheres with a row of cubic zirconia, for a stacked look in a single ring. Add texture and sparkle to everyday outfits or evenings out.
+• Material: 18K gold plated, with three layers of gold
+• Stones: 11 cubic zirconia, 2 mm
+• Row of nine 3 mm spheres
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X81" s="6" t="inlineStr"/>
+      <c r="Y81" s="7" t="inlineStr">
         <is>
           <t>Anel sem opção de tamanho: o código termina em ...1206, ou seja aro 12 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
@@ -8444,9 +9625,24 @@
       </c>
       <c r="T82" s="4" t="inlineStr"/>
       <c r="U82" s="4" t="inlineStr"/>
-      <c r="V82" s="4" t="inlineStr"/>
-      <c r="W82" s="6" t="inlineStr"/>
-      <c r="X82" s="7" t="inlineStr">
+      <c r="V82" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
+          <t>Slim butterfly ring plated in 18K gold and set with cubic zirconia in two sizes. Wear it as a dainty everyday ring or stack it with other fine bands for extra sparkle.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Three 1.5 mm and three 2.5 mm cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X82" s="6" t="inlineStr"/>
+      <c r="Y82" s="7" t="inlineStr">
         <is>
           <t>Anel sem opção de tamanho: o código termina em ...1606, ou seja aro 16 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
@@ -8544,9 +9740,23 @@
       </c>
       <c r="T83" s="4" t="inlineStr"/>
       <c r="U83" s="4" t="inlineStr"/>
-      <c r="V83" s="4" t="inlineStr"/>
-      <c r="W83" s="6" t="inlineStr"/>
-      <c r="X83" s="7" t="inlineStr">
+      <c r="V83" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W83" s="6" t="inlineStr">
+        <is>
+          <t>Personalised bar necklace plated in 18K gold, with a customisable pendant plate for a piece that feels truly yours. Give it for a birthday, a graduation or an anniversary.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X83" s="6" t="inlineStr"/>
+      <c r="Y83" s="7" t="inlineStr">
         <is>
           <t>Colar personalizável: explique na descrição como a cliente envia o nome (campo de texto ou mensagem).</t>
         </is>
@@ -8644,13 +9854,28 @@
       </c>
       <c r="T84" s="4" t="inlineStr"/>
       <c r="U84" s="4" t="inlineStr"/>
-      <c r="V84" s="4" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W84" s="6" t="inlineStr">
         <is>
+          <t>Heart earrings plated in 18K gold and set with crystals: a sparkling symbol of love to wear every day. A sweet gift for Valentine's Day, an anniversary or a best friend's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X84" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-heart-crystal-earrings-522372</t>
         </is>
       </c>
-      <c r="X84" s="4" t="inlineStr"/>
+      <c r="Y84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -8744,9 +9969,24 @@
       </c>
       <c r="T85" s="4" t="inlineStr"/>
       <c r="U85" s="4" t="inlineStr"/>
-      <c r="V85" s="4" t="inlineStr"/>
-      <c r="W85" s="6" t="inlineStr"/>
-      <c r="X85" s="4" t="inlineStr"/>
+      <c r="V85" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W85" s="6" t="inlineStr">
+        <is>
+          <t>Crystal and pearl drop earrings by Rommanel, pairing sparkling crystals with synthetic pearls in 18K gold plating. A graceful choice for weddings and dinners out, and a lovely bridesmaid gift.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Crystals and synthetic pearls
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X85" s="6" t="inlineStr"/>
+      <c r="Y85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -8836,9 +10076,24 @@
       <c r="S86" s="4" t="inlineStr"/>
       <c r="T86" s="4" t="inlineStr"/>
       <c r="U86" s="4" t="inlineStr"/>
-      <c r="V86" s="4" t="inlineStr"/>
-      <c r="W86" s="6" t="inlineStr"/>
-      <c r="X86" s="4" t="inlineStr"/>
+      <c r="V86" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W86" s="6" t="inlineStr">
+        <is>
+          <t>Curved statement earrings in 18K gold plating, set with cubic zirconia for a modern flash of sparkle. Wear them to dinners, parties and celebrations, or with a simple white shirt.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X86" s="6" t="inlineStr"/>
+      <c r="Y86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -8932,13 +10187,30 @@
       </c>
       <c r="T87" s="4" t="inlineStr"/>
       <c r="U87" s="4" t="inlineStr"/>
-      <c r="V87" s="4" t="inlineStr"/>
+      <c r="V87" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W87" s="6" t="inlineStr">
         <is>
+          <t>Minimalist ball pendant necklace: a 10 mm gold-plated sphere on a fine 45 cm Venetian chain. Simple enough for every day, and easy to layer with longer chains.
+• Material: 18K gold plated, with three layers of gold
+• Length: 45 cm
+• Venetian chain, 0.4 mm
+• 10 mm ball pendant
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X87" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-ball-pendant-necklace-45-cm-53254900</t>
         </is>
       </c>
-      <c r="X87" s="4" t="inlineStr"/>
+      <c r="Y87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -9028,9 +10300,25 @@
       <c r="S88" s="4" t="inlineStr"/>
       <c r="T88" s="4" t="inlineStr"/>
       <c r="U88" s="4" t="inlineStr"/>
-      <c r="V88" s="4" t="inlineStr"/>
-      <c r="W88" s="6" t="inlineStr"/>
-      <c r="X88" s="4" t="inlineStr"/>
+      <c r="V88" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W88" s="6" t="inlineStr">
+        <is>
+          <t>Glittering butterfly stud earrings paved with tiny cubic zirconia and plated in 18K gold, a pretty bit of sparkle for every day. Lovely as a birthday gift for a daughter, sister or friend.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.9 cm x 1.2 cm
+• Stones: 28 cubic zirconia per pair, 1 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X88" s="6" t="inlineStr"/>
+      <c r="Y88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -9120,9 +10408,26 @@
       <c r="S89" s="4" t="inlineStr"/>
       <c r="T89" s="4" t="inlineStr"/>
       <c r="U89" s="4" t="inlineStr"/>
-      <c r="V89" s="4" t="inlineStr"/>
-      <c r="W89" s="6" t="inlineStr"/>
-      <c r="X89" s="4" t="inlineStr"/>
+      <c r="V89" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W89" s="6" t="inlineStr">
+        <is>
+          <t>Two pairs in one set: triangle solitaire studs and hoop earrings, each earring holding a 4 mm triangular cubic zirconia, all in 18K gold plating. Style them together as an ear stack or wear each pair on its own.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.5 cm x 0.5 cm (studs), 2 cm x 0.5 cm (hoops)
+• Stones: Four triangular cubic zirconia, 4 mm x 4 mm, one per earring
+• Set of two pairs: triangle solitaire studs and hoop earrings
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X89" s="6" t="inlineStr"/>
+      <c r="Y89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -9212,9 +10517,24 @@
       <c r="S90" s="4" t="inlineStr"/>
       <c r="T90" s="4" t="inlineStr"/>
       <c r="U90" s="4" t="inlineStr"/>
-      <c r="V90" s="4" t="inlineStr"/>
-      <c r="W90" s="6" t="inlineStr"/>
-      <c r="X90" s="7" t="inlineStr">
+      <c r="V90" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W90" s="6" t="inlineStr">
+        <is>
+          <t>Half hoop earrings made of several smooth wires side by side, plated in 18K gold and measuring 1.3 cm. An easy everyday pair with more texture than a plain hoop.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X90" s="6" t="inlineStr"/>
+      <c r="Y90" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -9312,9 +10632,25 @@
       </c>
       <c r="T91" s="4" t="inlineStr"/>
       <c r="U91" s="4" t="inlineStr"/>
-      <c r="V91" s="4" t="inlineStr"/>
-      <c r="W91" s="6" t="inlineStr"/>
-      <c r="X91" s="4" t="inlineStr"/>
+      <c r="V91" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W91" s="6" t="inlineStr">
+        <is>
+          <t>Kids' star stud earrings, 0.5 cm, each with a single crystal set in 18K gold plating. A cute first pair for a little one's birthday or for Christmas.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.5 cm
+• Stones: One crystal per earring
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X91" s="6" t="inlineStr"/>
+      <c r="Y91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -9404,9 +10740,25 @@
       <c r="S92" s="4" t="inlineStr"/>
       <c r="T92" s="4" t="inlineStr"/>
       <c r="U92" s="4" t="inlineStr"/>
-      <c r="V92" s="4" t="inlineStr"/>
-      <c r="W92" s="6" t="inlineStr"/>
-      <c r="X92" s="4" t="inlineStr"/>
+      <c r="V92" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W92" s="6" t="inlineStr">
+        <is>
+          <t>Wavy openwork hoop earrings, 1.8 cm, that combine 18K gold plating with rhodium plating for a two-tone finish. A smart choice if you like to wear gold and silver tones together.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Size: 1.8 cm
+• Two-tone: 18K gold plating with rhodium plating
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X92" s="6" t="inlineStr"/>
+      <c r="Y92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -9496,13 +10848,29 @@
       <c r="S93" s="4" t="inlineStr"/>
       <c r="T93" s="4" t="inlineStr"/>
       <c r="U93" s="4" t="inlineStr"/>
-      <c r="V93" s="4" t="inlineStr"/>
+      <c r="V93" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W93" s="6" t="inlineStr">
         <is>
+          <t>Huggie hoop earrings set with cubic zirconia and plated in 18K gold, just 0.7 cm across. A small, sparkling pair to wear every day, alone or alongside your favourite studs.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.7 cm diameter
+• Stones: 10 cubic zirconia per pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X93" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-huggie-hoop-earrings-with-cubic-zirconia-52321406</t>
         </is>
       </c>
-      <c r="X93" s="7" t="inlineStr">
+      <c r="Y93" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -9596,9 +10964,25 @@
       <c r="S94" s="4" t="inlineStr"/>
       <c r="T94" s="4" t="inlineStr"/>
       <c r="U94" s="4" t="inlineStr"/>
-      <c r="V94" s="4" t="inlineStr"/>
-      <c r="W94" s="6" t="inlineStr"/>
-      <c r="X94" s="4" t="inlineStr"/>
+      <c r="V94" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W94" s="6" t="inlineStr">
+        <is>
+          <t>Statement ball drop earrings: hollow filigree spheres hanging one from another, plated in 18K gold. A playful, eye-catching pair for parties, weddings and summer evenings.
+• Material: 18K gold plated, with three layers of gold
+• Size: 4.4 cm x 1.2 cm
+• Hollow spheres hanging one from another
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X94" s="6" t="inlineStr"/>
+      <c r="Y94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -9690,13 +11074,25 @@
       <c r="U95" s="4" t="inlineStr"/>
       <c r="V95" s="4" t="inlineStr">
         <is>
-          <t>tirou 'Medical grade'</t>
-        </is>
-      </c>
-      <c r="W95" s="6" t="inlineStr"/>
-      <c r="X95" s="7" t="inlineStr">
-        <is>
-          <t>A descrição diz 'Medical grade' sem comprovação: a importação 2 tira essa frase.</t>
+          <t>descrição nova; tirou 'Medical grade'</t>
+        </is>
+      </c>
+      <c r="W95" s="6" t="inlineStr">
+        <is>
+          <t>Fine salamander chain choker by Rommanel, plated in 18K gold and 38 cm long. Clean and minimal on its own, or layered with longer necklaces and pendants.
+• Material: 18K gold plated, with three layers of gold
+• Length: 38 cm
+• Salamander chain, 1 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X95" s="6" t="inlineStr"/>
+      <c r="Y95" s="7" t="inlineStr">
+        <is>
+          <t>A descrição diz 'Medical grade' sem comprovação: a descrição nova da importação 2 não traz essa frase.</t>
         </is>
       </c>
     </row>
@@ -9792,9 +11188,24 @@
         </is>
       </c>
       <c r="U96" s="4" t="inlineStr"/>
-      <c r="V96" s="4" t="inlineStr"/>
-      <c r="W96" s="6" t="inlineStr"/>
-      <c r="X96" s="4" t="inlineStr"/>
+      <c r="V96" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W96" s="6" t="inlineStr">
+        <is>
+          <t>Double link bracelet in solid 925 sterling silver, 19 cm long: a classic chain design for everyday wear, on its own or stacked with a watch. A thoughtful birthday or anniversary gift.
+• Material: solid 925 sterling silver
+• Length: 19 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X96" s="6" t="inlineStr"/>
+      <c r="Y96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -9888,9 +11299,28 @@
         </is>
       </c>
       <c r="U97" s="4" t="inlineStr"/>
-      <c r="V97" s="4" t="inlineStr"/>
-      <c r="W97" s="6" t="inlineStr"/>
-      <c r="X97" s="4" t="inlineStr"/>
+      <c r="V97" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W97" s="6" t="inlineStr">
+        <is>
+          <t>Red heart pendant in solid 925 sterling silver, holding a single heart-shaped cubic zirconia in a solitaire setting. A loving gift for an anniversary or Valentine's Day.
+• Material: solid 925 sterling silver
+• Size: 1.2 cm x 0.6 cm
+• Stones: One red heart-shaped cubic zirconia, 4 mm x 4 mm
+• Solitaire setting
+• From the Cycles of Life Collection
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X97" s="6" t="inlineStr"/>
+      <c r="Y97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -9984,9 +11414,26 @@
         </is>
       </c>
       <c r="U98" s="4" t="inlineStr"/>
-      <c r="V98" s="4" t="inlineStr"/>
-      <c r="W98" s="6" t="inlineStr"/>
-      <c r="X98" s="4" t="inlineStr"/>
+      <c r="V98" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
+          <t>Versatile gourmet chain necklace in solid 925 sterling silver, 50 cm long, made of faceted curb-style links. Wear it alone as an everyday chain or layer it with shorter necklaces.
+• Material: solid 925 sterling silver
+• Length: 50 cm
+• Faceted gourmet (curb) chain, 0.35 mm wire
+• From the Eternally 925 Sterling Silver Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X98" s="6" t="inlineStr"/>
+      <c r="Y98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -10080,9 +11527,26 @@
         </is>
       </c>
       <c r="U99" s="4" t="inlineStr"/>
-      <c r="V99" s="4" t="inlineStr"/>
-      <c r="W99" s="6" t="inlineStr"/>
-      <c r="X99" s="4" t="inlineStr"/>
+      <c r="V99" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W99" s="6" t="inlineStr">
+        <is>
+          <t>Sterling silver butterfly studs decorated with raised bead detailing, 0.7 cm x 0.9 cm. A dainty, nature-inspired pair for everyday wear and a pretty gift for a friend or daughter.
+• Material: solid 925 sterling silver
+• Size: 0.7 cm x 0.9 cm
+• Raised bead detailing
+• From the Aurora Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X99" s="6" t="inlineStr"/>
+      <c r="Y99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -10176,9 +11640,27 @@
         </is>
       </c>
       <c r="U100" s="4" t="inlineStr"/>
-      <c r="V100" s="4" t="inlineStr"/>
-      <c r="W100" s="6" t="inlineStr"/>
-      <c r="X100" s="7" t="inlineStr">
+      <c r="V100" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W100" s="6" t="inlineStr">
+        <is>
+          <t>Solitaire teardrop stud earrings by Rommanel in solid 925 sterling silver, each holding a 5 mm x 7 mm pear-shaped cubic zirconia. Classic sparkle for weddings, graduations and evenings out.
+• Material: solid 925 sterling silver
+• Size: 0.9 cm x 0.7 cm
+• Stones: Two white teardrop cubic zirconia, 5 mm x 7 mm, one per earring
+• Solitaire setting
+• From the Aurora Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X100" s="6" t="inlineStr"/>
+      <c r="Y100" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -10276,9 +11758,26 @@
         </is>
       </c>
       <c r="U101" s="4" t="inlineStr"/>
-      <c r="V101" s="4" t="inlineStr"/>
-      <c r="W101" s="6" t="inlineStr"/>
-      <c r="X101" s="4" t="inlineStr"/>
+      <c r="V101" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W101" s="6" t="inlineStr">
+        <is>
+          <t>Tiny butterfly stud earrings in solid 925 sterling silver, set with cubic zirconia and measuring 0.6 cm x 0.6 cm. Suitable for grown-ups and kids, they make a sweet gift for a daughter or granddaughter.
+• Material: solid 925 sterling silver
+• Size: 0.6 cm x 0.6 cm
+• Stones: 10 cubic zirconia per pair, 1 mm
+• Suitable for adults and children
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X101" s="6" t="inlineStr"/>
+      <c r="Y101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -10376,9 +11875,26 @@
         </is>
       </c>
       <c r="U102" s="4" t="inlineStr"/>
-      <c r="V102" s="4" t="inlineStr"/>
-      <c r="W102" s="6" t="inlineStr"/>
-      <c r="X102" s="4" t="inlineStr"/>
+      <c r="V102" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W102" s="6" t="inlineStr">
+        <is>
+          <t>Simple 3 mm ball stud earrings in solid 925 sterling silver, for adults and children alike. A classic first pair for little ears and a discreet everyday stud for grown-ups.
+• Material: solid 925 sterling silver
+• Size: 3 mm diameter
+• Suitable for adults and children
+• From Rommanel's Permanent Line
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X102" s="6" t="inlineStr"/>
+      <c r="Y102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -10472,9 +11988,26 @@
         </is>
       </c>
       <c r="U103" s="4" t="inlineStr"/>
-      <c r="V103" s="4" t="inlineStr"/>
-      <c r="W103" s="6" t="inlineStr"/>
-      <c r="X103" s="4" t="inlineStr"/>
+      <c r="V103" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W103" s="6" t="inlineStr">
+        <is>
+          <t>Sparkling huggie hoops in solid 925 sterling silver, studded with cubic zirconia and 1.4 cm in outer diameter. A refined finishing touch for work, dinners and special occasions.
+• Material: solid 925 sterling silver
+• Size: 1.4 cm external diameter
+• Stones: 40 white cubic zirconia per pair, 1.25 mm
+• From Rommanel's Permanent Line
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X103" s="6" t="inlineStr"/>
+      <c r="Y103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -10568,9 +12101,25 @@
       </c>
       <c r="T104" s="4" t="inlineStr"/>
       <c r="U104" s="4" t="inlineStr"/>
-      <c r="V104" s="4" t="inlineStr"/>
-      <c r="W104" s="6" t="inlineStr"/>
-      <c r="X104" s="4" t="inlineStr"/>
+      <c r="V104" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W104" s="6" t="inlineStr">
+        <is>
+          <t>Little crown stud earrings for children, with an openwork design and granulated detail in 18K gold plating. A fun birthday gift for a young princess or prince.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.7 cm x 0.8 cm
+• Openwork crown with granulated detail
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X104" s="6" t="inlineStr"/>
+      <c r="Y104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -10664,9 +12213,23 @@
       </c>
       <c r="T105" s="4" t="inlineStr"/>
       <c r="U105" s="4" t="inlineStr"/>
-      <c r="V105" s="4" t="inlineStr"/>
-      <c r="W105" s="6" t="inlineStr"/>
-      <c r="X105" s="4" t="inlineStr"/>
+      <c r="V105" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W105" s="6" t="inlineStr">
+        <is>
+          <t>Children's bird drop earrings plated in 18K gold, a cheerful pair for little nature lovers. A charming birthday or Christmas gift for a granddaughter, niece or goddaughter.
+• Material: 18K gold plated, with three layers of gold
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X105" s="6" t="inlineStr"/>
+      <c r="Y105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -10756,9 +12319,24 @@
       <c r="S106" s="4" t="inlineStr"/>
       <c r="T106" s="4" t="inlineStr"/>
       <c r="U106" s="4" t="inlineStr"/>
-      <c r="V106" s="4" t="inlineStr"/>
-      <c r="W106" s="6" t="inlineStr"/>
-      <c r="X106" s="4" t="inlineStr"/>
+      <c r="V106" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W106" s="6" t="inlineStr">
+        <is>
+          <t>Pavé heart stud earrings in 18K gold plating, set with 20 cubic zirconia across the pair. A sparkling everyday reminder of love, and a lovely gift for Mother's Day or a birthday.
+• Material: 18K gold plated, with three layers of gold
+• Stones: 20 cubic zirconia per pair
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X106" s="6" t="inlineStr"/>
+      <c r="Y106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -10848,9 +12426,24 @@
       <c r="S107" s="4" t="inlineStr"/>
       <c r="T107" s="4" t="inlineStr"/>
       <c r="U107" s="4" t="inlineStr"/>
-      <c r="V107" s="4" t="inlineStr"/>
-      <c r="W107" s="6" t="inlineStr"/>
-      <c r="X107" s="7" t="inlineStr">
+      <c r="V107" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W107" s="6" t="inlineStr">
+        <is>
+          <t>Half hoop earrings paved with cubic zirconia and plated in 18K gold, for a touch of sparkle from morning meetings to evenings out. Wear them solo or with simple studs.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X107" s="6" t="inlineStr"/>
+      <c r="Y107" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -10944,9 +12537,24 @@
       <c r="S108" s="4" t="inlineStr"/>
       <c r="T108" s="4" t="inlineStr"/>
       <c r="U108" s="4" t="inlineStr"/>
-      <c r="V108" s="4" t="inlineStr"/>
-      <c r="W108" s="6" t="inlineStr"/>
-      <c r="X108" s="7" t="inlineStr">
+      <c r="V108" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W108" s="6" t="inlineStr">
+        <is>
+          <t>Smooth half hoop earrings plated in 18K gold, 1.3 cm: a clean, minimal shape that suits every day and pairs easily with studs and huggies.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X108" s="6" t="inlineStr"/>
+      <c r="Y108" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -11044,9 +12652,25 @@
       </c>
       <c r="T109" s="4" t="inlineStr"/>
       <c r="U109" s="4" t="inlineStr"/>
-      <c r="V109" s="4" t="inlineStr"/>
-      <c r="W109" s="6" t="inlineStr"/>
-      <c r="X109" s="4" t="inlineStr"/>
+      <c r="V109" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W109" s="6" t="inlineStr">
+        <is>
+          <t>Beaded bracelet for kids, made of 2 mm beads in 18K gold plating and measuring 14 cm. A lovely keepsake gift for a birthday or Christmas.
+• Material: 18K gold plated, with three layers of gold
+• Length: 14 cm
+• Made of 2 mm beads
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X109" s="6" t="inlineStr"/>
+      <c r="Y109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -11136,9 +12760,25 @@
       <c r="S110" s="4" t="inlineStr"/>
       <c r="T110" s="4" t="inlineStr"/>
       <c r="U110" s="4" t="inlineStr"/>
-      <c r="V110" s="4" t="inlineStr"/>
-      <c r="W110" s="6" t="inlineStr"/>
-      <c r="X110" s="4" t="inlineStr"/>
+      <c r="V110" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W110" s="6" t="inlineStr">
+        <is>
+          <t>Geometric link necklace by Rommanel, made of hammered rhombus-shaped links in 18K gold plating and 42 cm long. A modern chain to wear on its own or layer with finer necklaces.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Hammered rhombus-shaped links
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X110" s="6" t="inlineStr"/>
+      <c r="Y110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -11228,9 +12868,26 @@
       <c r="S111" s="4" t="inlineStr"/>
       <c r="T111" s="4" t="inlineStr"/>
       <c r="U111" s="4" t="inlineStr"/>
-      <c r="V111" s="4" t="inlineStr"/>
-      <c r="W111" s="6" t="inlineStr"/>
-      <c r="X111" s="7" t="inlineStr">
+      <c r="V111" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W111" s="6" t="inlineStr">
+        <is>
+          <t>Delicate lock chain necklace plated in 18K gold, 42 cm long and finished with a padlock clasp. Easy to layer with other chains or to wear on its own.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Lock chain, 0.2 mm
+• Padlock clasp
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X111" s="6" t="inlineStr"/>
+      <c r="Y111" s="7" t="inlineStr">
         <is>
           <t>Parece ser o mesmo colar do #21 (mesmo código-base 531638, mesma descrição). Mantenha um só e crie um redirecionamento do outro.</t>
         </is>
@@ -11324,9 +12981,24 @@
       <c r="S112" s="4" t="inlineStr"/>
       <c r="T112" s="4" t="inlineStr"/>
       <c r="U112" s="4" t="inlineStr"/>
-      <c r="V112" s="4" t="inlineStr"/>
-      <c r="W112" s="6" t="inlineStr"/>
-      <c r="X112" s="7" t="inlineStr">
+      <c r="V112" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W112" s="6" t="inlineStr">
+        <is>
+          <t>Black butterfly stud earrings set with synthetic stones and plated in 18K gold, a bold, graphic take on a much-loved motif. A great gift for a friend who loves butterflies.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Synthetic stones
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X112" s="6" t="inlineStr"/>
+      <c r="Y112" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -11420,9 +13092,24 @@
       <c r="S113" s="4" t="inlineStr"/>
       <c r="T113" s="4" t="inlineStr"/>
       <c r="U113" s="4" t="inlineStr"/>
-      <c r="V113" s="4" t="inlineStr"/>
-      <c r="W113" s="6" t="inlineStr"/>
-      <c r="X113" s="7" t="inlineStr">
+      <c r="V113" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W113" s="6" t="inlineStr">
+        <is>
+          <t>White butterfly stud earrings set with synthetic stones in 18K gold plating, a fresh and delicate everyday pair. A pretty gift for a birthday, a bridesmaid or a new graduate.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Synthetic stones
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X113" s="6" t="inlineStr"/>
+      <c r="Y113" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -11516,13 +13203,29 @@
       <c r="S114" s="4" t="inlineStr"/>
       <c r="T114" s="4" t="inlineStr"/>
       <c r="U114" s="4" t="inlineStr"/>
-      <c r="V114" s="4" t="inlineStr"/>
+      <c r="V114" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W114" s="6" t="inlineStr">
         <is>
+          <t>Domed teardrop stud earrings with a smooth 18K gold-plated surface, measuring 1.5 cm x 0.9 cm. A clean, modern shape to wear with jeans or dress up for the evening.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.5 cm x 0.9 cm
+• Domed, smooth surface
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X114" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-teardrop-stud-earrings-52747800</t>
         </is>
       </c>
-      <c r="X114" s="4" t="inlineStr"/>
+      <c r="Y114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -11612,9 +13315,24 @@
       <c r="S115" s="4" t="inlineStr"/>
       <c r="T115" s="4" t="inlineStr"/>
       <c r="U115" s="4" t="inlineStr"/>
-      <c r="V115" s="4" t="inlineStr"/>
-      <c r="W115" s="6" t="inlineStr"/>
-      <c r="X115" s="7" t="inlineStr">
+      <c r="V115" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W115" s="6" t="inlineStr">
+        <is>
+          <t>Bold 8 mm ball stud earrings plated in 18K gold: a simple round shape with real presence. Wear them on their own or with a fine chain for a neat, put-together look.
+• Material: 18K gold plated, with three layers of gold
+• Size: 8 mm diameter
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X115" s="6" t="inlineStr"/>
+      <c r="Y115" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -11708,9 +13426,24 @@
       <c r="S116" s="4" t="inlineStr"/>
       <c r="T116" s="4" t="inlineStr"/>
       <c r="U116" s="4" t="inlineStr"/>
-      <c r="V116" s="4" t="inlineStr"/>
-      <c r="W116" s="6" t="inlineStr"/>
-      <c r="X116" s="7" t="inlineStr">
+      <c r="V116" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W116" s="6" t="inlineStr">
+        <is>
+          <t>Dainty 4 mm ball stud earrings in 18K gold plating, a minimal everyday pair for a first or second piercing. Quiet enough for the office and easy to mix with hoops.
+• Material: 18K gold plated, with three layers of gold
+• Size: 4 mm diameter
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X116" s="6" t="inlineStr"/>
+      <c r="Y116" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -11804,9 +13537,25 @@
       <c r="S117" s="4" t="inlineStr"/>
       <c r="T117" s="4" t="inlineStr"/>
       <c r="U117" s="4" t="inlineStr"/>
-      <c r="V117" s="4" t="inlineStr"/>
-      <c r="W117" s="6" t="inlineStr"/>
-      <c r="X117" s="4" t="inlineStr"/>
+      <c r="V117" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W117" s="6" t="inlineStr">
+        <is>
+          <t>Openwork hoop earrings, 1.4 cm, patterned with cut-out squares and plated in 18K gold. A small hoop with a geometric twist that goes from casual days to dinner plans.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.4 cm
+• Openwork squares
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X117" s="6" t="inlineStr"/>
+      <c r="Y117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -11896,9 +13645,24 @@
       <c r="S118" s="4" t="inlineStr"/>
       <c r="T118" s="4" t="inlineStr"/>
       <c r="U118" s="4" t="inlineStr"/>
-      <c r="V118" s="4" t="inlineStr"/>
-      <c r="W118" s="6" t="inlineStr"/>
-      <c r="X118" s="7" t="inlineStr">
+      <c r="V118" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W118" s="6" t="inlineStr">
+        <is>
+          <t>Plain 1.7 cm hoop earrings plated in 18K gold, the kind of simple, versatile pair you reach for every morning. Wear them alone or alongside studs and ear cuffs.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.7 cm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X118" s="6" t="inlineStr"/>
+      <c r="Y118" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -12000,9 +13764,25 @@
           <t>N, P, R, T1/2, V1/2, Y, Z+1</t>
         </is>
       </c>
-      <c r="V119" s="4" t="inlineStr"/>
-      <c r="W119" s="6" t="inlineStr"/>
-      <c r="X119" s="4" t="inlineStr"/>
+      <c r="V119" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W119" s="6" t="inlineStr">
+        <is>
+          <t>Sixteen 1.5 mm cubic zirconia line the front of this half eternity ring in solid 925 sterling silver. Beautiful on its own or stacked with other bands, and a meaningful anniversary gift.
+• Material: solid 925 sterling silver
+• Stones: 16 cubic zirconia, 1.5 mm
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X119" s="6" t="inlineStr"/>
+      <c r="Y119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
@@ -12096,9 +13876,26 @@
         </is>
       </c>
       <c r="U120" s="4" t="inlineStr"/>
-      <c r="V120" s="4" t="inlineStr"/>
-      <c r="W120" s="6" t="inlineStr"/>
-      <c r="X120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W120" s="6" t="inlineStr">
+        <is>
+          <t>Faceted gourmet chain necklace in solid 925 sterling silver, 42 cm long, with curb-style links. A clean, classic everyday chain and an easy gift for a birthday or graduation.
+• Material: solid 925 sterling silver
+• Length: 42 cm
+• Faceted gourmet (curb) chain, 0.35 mm wire
+• From the Eternally 925 Sterling Silver Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X120" s="6" t="inlineStr"/>
+      <c r="Y120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -12192,9 +13989,27 @@
         </is>
       </c>
       <c r="U121" s="4" t="inlineStr"/>
-      <c r="V121" s="4" t="inlineStr"/>
-      <c r="W121" s="6" t="inlineStr"/>
-      <c r="X121" s="4" t="inlineStr"/>
+      <c r="V121" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W121" s="6" t="inlineStr">
+        <is>
+          <t>Fresh green teardrop pendant by Rommanel in solid 925 sterling silver, with a 4 mm x 6 mm teardrop cubic zirconia at the centre and 18 smaller stones. A lovely pop of colour for everyday outfits.
+• Material: solid 925 sterling silver
+• Size: 1.6 cm x 0.7 cm
+• Stones: One teardrop cubic zirconia, 4 mm x 6 mm, and 18 cubic zirconia, 1 mm
+• From the Eternally 925 Sterling Silver Collection
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X121" s="6" t="inlineStr"/>
+      <c r="Y121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -12288,9 +14103,26 @@
         </is>
       </c>
       <c r="U122" s="4" t="inlineStr"/>
-      <c r="V122" s="4" t="inlineStr"/>
-      <c r="W122" s="6" t="inlineStr"/>
-      <c r="X122" s="7" t="inlineStr">
+      <c r="V122" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W122" s="6" t="inlineStr">
+        <is>
+          <t>Green teardrop stud earrings in solid 925 sterling silver, each set with a 4 mm x 6 mm teardrop cubic zirconia and tiny accent stones. Colourful enough for weddings and parties, yet easy to wear every day.
+• Material: solid 925 sterling silver
+• Size: 0.9 cm x 0.7 cm
+• Stones: Per pair: two teardrop cubic zirconia, 4 mm x 6 mm, and 36 cubic zirconia, 1 mm
+• From the Eternally 925 Sterling Silver Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X122" s="6" t="inlineStr"/>
+      <c r="Y122" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -12392,9 +14224,25 @@
           <t>N, P, R, T1/2, V1/2, Y, Z+1</t>
         </is>
       </c>
-      <c r="V123" s="4" t="inlineStr"/>
-      <c r="W123" s="6" t="inlineStr"/>
-      <c r="X123" s="7" t="inlineStr">
+      <c r="V123" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W123" s="6" t="inlineStr">
+        <is>
+          <t>A 6 mm cubic zirconia takes centre stage on this solitaire ring in solid 925 sterling silver, joined by two 3 mm stones and 14 tiny accents. A classic choice for anniversaries or a promise ring.
+• Material: solid 925 sterling silver
+• Stones: White cubic zirconia: one 6 mm, two 3 mm and 14 at 1 mm
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X123" s="6" t="inlineStr"/>
+      <c r="Y123" s="7" t="inlineStr">
         <is>
           <t>Anel de prata 925 com o código 510139, que é o mesmo do anel banhado a ouro (#122). Códigos de prata da Rommanel começam com 8: confira o código certo.</t>
         </is>
@@ -12492,9 +14340,25 @@
           <t>N, P, R, V1/2, T1/2, Y, Z+1</t>
         </is>
       </c>
-      <c r="V124" s="4" t="inlineStr"/>
-      <c r="W124" s="6" t="inlineStr"/>
-      <c r="X124" s="4" t="inlineStr"/>
+      <c r="V124" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W124" s="6" t="inlineStr">
+        <is>
+          <t>Elegant solitaire ring plated in 18K gold and set with cubic zirconia, a classic engagement-style design for everyday wear. A lovely gift for an anniversary or birthday.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X124" s="6" t="inlineStr"/>
+      <c r="Y124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -12588,9 +14452,25 @@
           <t>Y, R, Z+1, V1/2, T1/2, N, P</t>
         </is>
       </c>
-      <c r="V125" s="4" t="inlineStr"/>
-      <c r="W125" s="6" t="inlineStr"/>
-      <c r="X125" s="4" t="inlineStr"/>
+      <c r="V125" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W125" s="6" t="inlineStr">
+        <is>
+          <t>Half eternity ring plated in 18K gold, with cubic zirconia set halfway around the band. Wear it alone every day, or stack it with your favourite rings for extra sparkle.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X125" s="6" t="inlineStr"/>
+      <c r="Y125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
@@ -12684,9 +14564,25 @@
           <t>P, N, Y, R, Z+1, V1/2, T1/2</t>
         </is>
       </c>
-      <c r="V126" s="4" t="inlineStr"/>
-      <c r="W126" s="6" t="inlineStr"/>
-      <c r="X126" s="4" t="inlineStr"/>
+      <c r="V126" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W126" s="6" t="inlineStr">
+        <is>
+          <t>Pavé disc ring by Rommanel with an 18K gold-plated finish, its round face covered in sparkling cubic zirconia. A bright everyday ring to wear on its own or next to plain gold bands.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Cubic zirconia
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X126" s="6" t="inlineStr"/>
+      <c r="Y126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -12780,9 +14676,25 @@
           <t>P, Y, R, Z+1, V1/2, T1/2, N</t>
         </is>
       </c>
-      <c r="V127" s="4" t="inlineStr"/>
-      <c r="W127" s="6" t="inlineStr"/>
-      <c r="X127" s="4" t="inlineStr"/>
+      <c r="V127" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W127" s="6" t="inlineStr">
+        <is>
+          <t>Statement halo ring plated in 18K gold, with a red crystal at its centre framed by cubic zirconia. A bold flash of colour for parties, dinners out and special occasions.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Red crystal and cubic zirconia
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X127" s="6" t="inlineStr"/>
+      <c r="Y127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -12872,9 +14784,25 @@
       <c r="S128" s="4" t="inlineStr"/>
       <c r="T128" s="4" t="inlineStr"/>
       <c r="U128" s="4" t="inlineStr"/>
-      <c r="V128" s="4" t="inlineStr"/>
-      <c r="W128" s="6" t="inlineStr"/>
-      <c r="X128" s="7" t="inlineStr">
+      <c r="V128" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W128" s="6" t="inlineStr">
+        <is>
+          <t>Faceted heart-shaped links form this gold-plated heart bracelet, 19 cm long and adjustable to 18 cm. A sweet gift for someone you love, from Valentine's Day to birthdays.
+• Material: 18K gold plated, with three layers of gold
+• Length: 19 cm, adjustable to 18 cm
+• Chain of faceted heart-shaped links
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X128" s="6" t="inlineStr"/>
+      <c r="Y128" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -12968,9 +14896,26 @@
       <c r="S129" s="4" t="inlineStr"/>
       <c r="T129" s="4" t="inlineStr"/>
       <c r="U129" s="4" t="inlineStr"/>
-      <c r="V129" s="4" t="inlineStr"/>
-      <c r="W129" s="6" t="inlineStr"/>
-      <c r="X129" s="7" t="inlineStr">
+      <c r="V129" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W129" s="6" t="inlineStr">
+        <is>
+          <t>Y necklace plated in 18K gold: a fine 70 cm adjustable chain set with five 5 mm cubic zirconia and finished with a sixth stone at the end. Lovely with V-necks and open collars.
+• Material: 18K gold plated, with three layers of gold
+• Length: 70 cm, adjustable
+• Stones: Five 5 mm cubic zirconia, plus one at the end
+• Laminated link chain, 0.35 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X129" s="6" t="inlineStr"/>
+      <c r="Y129" s="7" t="inlineStr">
         <is>
           <t>Estava com o tipo EARRINGS, mas é um colar (Y necklace).</t>
         </is>
@@ -13064,9 +15009,25 @@
       <c r="S130" s="4" t="inlineStr"/>
       <c r="T130" s="4" t="inlineStr"/>
       <c r="U130" s="4" t="inlineStr"/>
-      <c r="V130" s="4" t="inlineStr"/>
-      <c r="W130" s="6" t="inlineStr"/>
-      <c r="X130" s="7" t="inlineStr">
+      <c r="V130" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W130" s="6" t="inlineStr">
+        <is>
+          <t>Small textured gold-plated hoop earrings, 1.1 cm across, with raised detailing that adds interest to a classic hoop. A neat pair for every day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.1 cm diameter
+• Raised detailing on the hoop
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X130" s="6" t="inlineStr"/>
+      <c r="Y130" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -13160,9 +15121,25 @@
       <c r="S131" s="4" t="inlineStr"/>
       <c r="T131" s="4" t="inlineStr"/>
       <c r="U131" s="4" t="inlineStr"/>
-      <c r="V131" s="4" t="inlineStr"/>
-      <c r="W131" s="6" t="inlineStr"/>
-      <c r="X131" s="4" t="inlineStr"/>
+      <c r="V131" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W131" s="6" t="inlineStr">
+        <is>
+          <t>Two-tone hoop earrings by Rommanel, plated in 18K gold with rhodium plating for a mix of gold and silver tones, measuring 1.9 cm x 0.7 cm. A simple way to wear gold and silver jewellery together.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Size: 1.9 cm x 0.7 cm
+• Two-tone: 18K gold plating with rhodium plating
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X131" s="6" t="inlineStr"/>
+      <c r="Y131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -13252,9 +15229,25 @@
       <c r="S132" s="4" t="inlineStr"/>
       <c r="T132" s="4" t="inlineStr"/>
       <c r="U132" s="4" t="inlineStr"/>
-      <c r="V132" s="4" t="inlineStr"/>
-      <c r="W132" s="6" t="inlineStr"/>
-      <c r="X132" s="4" t="inlineStr"/>
+      <c r="V132" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W132" s="6" t="inlineStr">
+        <is>
+          <t>Round pavé stud earrings plated in 18K gold, each 0.7 cm stud covered in 1.25 mm cubic zirconia. Small enough for every day, with enough sparkle for evenings out.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.7 cm diameter
+• Stones: 38 cubic zirconia per pair, 1.25 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X132" s="6" t="inlineStr"/>
+      <c r="Y132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -13344,9 +15337,26 @@
       <c r="S133" s="4" t="inlineStr"/>
       <c r="T133" s="4" t="inlineStr"/>
       <c r="U133" s="4" t="inlineStr"/>
-      <c r="V133" s="4" t="inlineStr"/>
-      <c r="W133" s="6" t="inlineStr"/>
-      <c r="X133" s="4" t="inlineStr"/>
+      <c r="V133" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W133" s="6" t="inlineStr">
+        <is>
+          <t>Solitaire stud earring set with two pairs in 18K gold plate: a small pair with 2 mm cubic zirconia and a larger pair with 5 mm stones. Wear them together in two piercings or one pair at a time.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.4 cm and 0.6 cm diameter
+• Stones: Two round 2 mm cubic zirconia and two 5 mm cubic zirconia
+• Set of two pairs of solitaire studs in two sizes
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X133" s="6" t="inlineStr"/>
+      <c r="Y133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
@@ -13436,9 +15446,26 @@
       <c r="S134" s="4" t="inlineStr"/>
       <c r="T134" s="4" t="inlineStr"/>
       <c r="U134" s="4" t="inlineStr"/>
-      <c r="V134" s="4" t="inlineStr"/>
-      <c r="W134" s="6" t="inlineStr"/>
-      <c r="X134" s="4" t="inlineStr"/>
+      <c r="V134" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W134" s="6" t="inlineStr">
+        <is>
+          <t>Arrow and heart earring set in 18K gold plate, pairing little arrow studs with heart-shaped cubic zirconia solitaires. Mix and match them, or give them to a best friend or on Valentine's Day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.4 cm x 1 cm (arrow), 0.5 cm x 0.5 cm (heart)
+• Stones: Two heart-shaped cubic zirconia, 4 mm x 4 mm
+• Set of two pairs: arrow studs and heart solitaire studs
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X134" s="6" t="inlineStr"/>
+      <c r="Y134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -13532,9 +15559,25 @@
           <t>Y, R, Z+1, V1/2, T1/2, N, P</t>
         </is>
       </c>
-      <c r="V135" s="4" t="inlineStr"/>
-      <c r="W135" s="6" t="inlineStr"/>
-      <c r="X135" s="4" t="inlineStr"/>
+      <c r="V135" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W135" s="6" t="inlineStr">
+        <is>
+          <t>Wide twisted band ring plated in 18K gold, a bold statement piece from Rommanel's Permanent Line. Wear it on its own or let it anchor a stack of finer rings.
+• Material: 18K gold plated, with three layers of gold
+• From Rommanel's Permanent Line
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X135" s="6" t="inlineStr"/>
+      <c r="Y135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -13628,9 +15671,26 @@
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr"/>
-      <c r="V136" s="4" t="inlineStr"/>
-      <c r="W136" s="6" t="inlineStr"/>
-      <c r="X136" s="4" t="inlineStr"/>
+      <c r="V136" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W136" s="6" t="inlineStr">
+        <is>
+          <t>Teardrop hoop earrings in solid 925 sterling silver, smooth and simple at 1.6 cm x 1 cm. An everyday pair from Rommanel's Permanent Line, for workdays and weekends alike.
+• Material: solid 925 sterling silver
+• Size: 1.6 cm x 1 cm
+• Smooth finish
+• From Rommanel's Permanent Line
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X136" s="6" t="inlineStr"/>
+      <c r="Y136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -13724,9 +15784,28 @@
         </is>
       </c>
       <c r="U137" s="4" t="inlineStr"/>
-      <c r="V137" s="4" t="inlineStr"/>
-      <c r="W137" s="6" t="inlineStr"/>
-      <c r="X137" s="4" t="inlineStr"/>
+      <c r="V137" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W137" s="6" t="inlineStr">
+        <is>
+          <t>Solid 925 sterling silver teardrop necklace, the pendant set with cubic zirconia and hung on a 50 cm Venetian chain. Openwork flowers decorate the back, a pretty detail just for the wearer.
+• Material: solid 925 sterling silver
+• Length: 50 cm
+• Stones: 13 cubic zirconia, 1 mm
+• Venetian chain, 0.8 mm
+• Openwork flowers on the back of the pendant
+• From the Time Capsule Collection
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X137" s="6" t="inlineStr"/>
+      <c r="Y137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
@@ -13816,9 +15895,24 @@
       <c r="S138" s="4" t="inlineStr"/>
       <c r="T138" s="4" t="inlineStr"/>
       <c r="U138" s="4" t="inlineStr"/>
-      <c r="V138" s="4" t="inlineStr"/>
-      <c r="W138" s="6" t="inlineStr"/>
-      <c r="X138" s="4" t="inlineStr"/>
+      <c r="V138" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W138" s="6" t="inlineStr">
+        <is>
+          <t>Tennis bracelet plated in 18K gold and lined with sparkling crystals. A classic choice for weddings and formal events, it also dresses up a simple everyday outfit.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X138" s="6" t="inlineStr"/>
+      <c r="Y138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -13908,9 +16002,27 @@
       <c r="S139" s="4" t="inlineStr"/>
       <c r="T139" s="4" t="inlineStr"/>
       <c r="U139" s="4" t="inlineStr"/>
-      <c r="V139" s="4" t="inlineStr"/>
-      <c r="W139" s="6" t="inlineStr"/>
-      <c r="X139" s="4" t="inlineStr"/>
+      <c r="V139" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W139" s="6" t="inlineStr">
+        <is>
+          <t>Boy mum bracelet finished in 18K gold plating: a fine 19 cm chain with a little boy charm, a square cubic zirconia and a cubic zirconia heart. A lovely gift for a new mum, a baby shower or Mother's Day.
+• Material: 18K gold plated, with three layers of gold
+• Length: 19 cm, adjustable to 18 cm
+• Stones: One 3 mm x 3 mm square-cut and one 5 mm x 5 mm heart-shaped cubic zirconia
+• Laminated link chain, 0.35 mm
+• Boy charm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X139" s="6" t="inlineStr"/>
+      <c r="Y139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
@@ -14000,9 +16112,25 @@
       <c r="S140" s="4" t="inlineStr"/>
       <c r="T140" s="4" t="inlineStr"/>
       <c r="U140" s="4" t="inlineStr"/>
-      <c r="V140" s="4" t="inlineStr"/>
-      <c r="W140" s="6" t="inlineStr"/>
-      <c r="X140" s="4" t="inlineStr"/>
+      <c r="V140" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W140" s="6" t="inlineStr">
+        <is>
+          <t>Best friends rainbow pendants plated in 18K gold with resin detail, made to celebrate a friendship. A happy gift for a birthday, a farewell or just because.
+• Material: 18K gold plated, with three layers of gold
+• Resin detail
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X140" s="6" t="inlineStr"/>
+      <c r="Y140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -14092,9 +16220,24 @@
       <c r="S141" s="4" t="inlineStr"/>
       <c r="T141" s="4" t="inlineStr"/>
       <c r="U141" s="4" t="inlineStr"/>
-      <c r="V141" s="4" t="inlineStr"/>
-      <c r="W141" s="6" t="inlineStr"/>
-      <c r="X141" s="4" t="inlineStr"/>
+      <c r="V141" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W141" s="6" t="inlineStr">
+        <is>
+          <t>Blue crystal stud earrings plated in 18K gold, each with a single square crystal in a solitaire setting. A pop of colour for every day, or a bride's something blue.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Blue square crystals, one per earring
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X141" s="6" t="inlineStr"/>
+      <c r="Y141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -14184,9 +16327,25 @@
       <c r="S142" s="4" t="inlineStr"/>
       <c r="T142" s="4" t="inlineStr"/>
       <c r="U142" s="4" t="inlineStr"/>
-      <c r="V142" s="4" t="inlineStr"/>
-      <c r="W142" s="6" t="inlineStr"/>
-      <c r="X142" s="4" t="inlineStr"/>
+      <c r="V142" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W142" s="6" t="inlineStr">
+        <is>
+          <t>Clip-on ear cuff plated in 18K gold, set with a green crystal and cubic zirconia. It needs no piercing, so it's an easy way to add colour and sparkle to an ear stack.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Green crystal and cubic zirconia
+• Clip-on, no piercing needed
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X142" s="6" t="inlineStr"/>
+      <c r="Y142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -14276,9 +16435,24 @@
       <c r="S143" s="4" t="inlineStr"/>
       <c r="T143" s="4" t="inlineStr"/>
       <c r="U143" s="4" t="inlineStr"/>
-      <c r="V143" s="4" t="inlineStr"/>
-      <c r="W143" s="6" t="inlineStr"/>
-      <c r="X143" s="7" t="inlineStr">
+      <c r="V143" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W143" s="6" t="inlineStr">
+        <is>
+          <t>Green cubic zirconia bring colour to these 18K gold-plated half hoop earrings, a fresh take on a classic shape. Lovely with neutral outfits, or as a gift for someone who loves green.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Green cubic zirconia
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X143" s="6" t="inlineStr"/>
+      <c r="Y143" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -14376,9 +16550,25 @@
           <t>Y, R, Z+1, V1/2, T1/2, N, P</t>
         </is>
       </c>
-      <c r="V144" s="4" t="inlineStr"/>
-      <c r="W144" s="6" t="inlineStr"/>
-      <c r="X144" s="4" t="inlineStr"/>
+      <c r="V144" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W144" s="6" t="inlineStr">
+        <is>
+          <t>Double band ring plated in 18K gold and set with a blue crystal, giving the look of two bands worn together. Wear it for evenings out, or give it to someone whose favourite colour is blue.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Blue crystal
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X144" s="6" t="inlineStr"/>
+      <c r="Y144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -14472,9 +16662,25 @@
           <t>Y, R, Z+1, V1/2, T1/2, N, P</t>
         </is>
       </c>
-      <c r="V145" s="4" t="inlineStr"/>
-      <c r="W145" s="6" t="inlineStr"/>
-      <c r="X145" s="7" t="inlineStr">
+      <c r="V145" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W145" s="6" t="inlineStr">
+        <is>
+          <t>Black crystal heart ring in 18K gold plate: a single heart-shaped stone in a solitaire setting, romantic with a darker edge. A thoughtful gift for Valentine's Day or an anniversary.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Black heart-shaped crystal
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X145" s="6" t="inlineStr"/>
+      <c r="Y145" s="7" t="inlineStr">
         <is>
           <t>A descrição diz 'Size: 16 (BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
         </is>
@@ -14572,9 +16778,25 @@
           <t>Y, R, Z+1, V1/2, T1/2, N, P</t>
         </is>
       </c>
-      <c r="V146" s="4" t="inlineStr"/>
-      <c r="W146" s="6" t="inlineStr"/>
-      <c r="X146" s="7" t="inlineStr">
+      <c r="V146" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W146" s="6" t="inlineStr">
+        <is>
+          <t>Sparkling blue crystal ring with an 18K gold-plated finish, accented with cubic zirconia. A statement piece for dinners, parties and celebrations, or worn beside simple gold bands.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Blue crystal and cubic zirconia
+• Australian ring sizes, with the Brazilian aro in our size guide
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X146" s="6" t="inlineStr"/>
+      <c r="Y146" s="7" t="inlineStr">
         <is>
           <t>A descrição diz 'Size: 14(BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
         </is>
@@ -14668,9 +16890,26 @@
       <c r="S147" s="4" t="inlineStr"/>
       <c r="T147" s="4" t="inlineStr"/>
       <c r="U147" s="4" t="inlineStr"/>
-      <c r="V147" s="4" t="inlineStr"/>
-      <c r="W147" s="6" t="inlineStr"/>
-      <c r="X147" s="4" t="inlineStr"/>
+      <c r="V147" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W147" s="6" t="inlineStr">
+        <is>
+          <t>Gold-plated butterfly bracelet with four shiny white resin butterflies on a fine 0.4 mm chain, 19 cm and adjustable to 17 cm. A pretty gift for a sister or friend who loves butterflies.
+• Material: 18K gold plated, with three layers of gold
+• Length: 19 cm, adjustable to 17 cm
+• Stones: Four white butterfly-shaped resin stones
+• Laminated link chain, 0.4 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X147" s="6" t="inlineStr"/>
+      <c r="Y147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
@@ -14760,9 +16999,25 @@
       <c r="S148" s="4" t="inlineStr"/>
       <c r="T148" s="4" t="inlineStr"/>
       <c r="U148" s="4" t="inlineStr"/>
-      <c r="V148" s="4" t="inlineStr"/>
-      <c r="W148" s="6" t="inlineStr"/>
-      <c r="X148" s="4" t="inlineStr"/>
+      <c r="V148" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W148" s="6" t="inlineStr">
+        <is>
+          <t>Twisted oval links make up this 18K gold-plated bracelet, adjustable from 19 cm to 17 cm. Wear it alone as a classic everyday piece, or stack it with other bracelets and a watch.
+• Material: 18K gold plated, with three layers of gold
+• Length: 19 cm, adjustable to 17 cm
+• Twisted oval links
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X148" s="6" t="inlineStr"/>
+      <c r="Y148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -14852,9 +17107,27 @@
       <c r="S149" s="4" t="inlineStr"/>
       <c r="T149" s="4" t="inlineStr"/>
       <c r="U149" s="4" t="inlineStr"/>
-      <c r="V149" s="4" t="inlineStr"/>
-      <c r="W149" s="6" t="inlineStr"/>
-      <c r="X149" s="4" t="inlineStr"/>
+      <c r="V149" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W149" s="6" t="inlineStr">
+        <is>
+          <t>Purple navette-cut cubic zirconia sparkle on one side of this butterfly pendant, plated in 18K gold and measuring 2 cm x 1.3 cm. Add it to a favourite chain for a touch of colour every day.
+• Material: 18K gold plated, with three layers of gold
+• Size: 2 cm x 1.3 cm
+• Stones: Two purple navette (marquise) cubic zirconia, 4 mm x 8 mm and 3 mm x 6 mm
+• Stones set on one side of the butterfly
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X149" s="6" t="inlineStr"/>
+      <c r="Y149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -14944,9 +17217,26 @@
       <c r="S150" s="4" t="inlineStr"/>
       <c r="T150" s="4" t="inlineStr"/>
       <c r="U150" s="4" t="inlineStr"/>
-      <c r="V150" s="4" t="inlineStr"/>
-      <c r="W150" s="6" t="inlineStr"/>
-      <c r="X150" s="4" t="inlineStr"/>
+      <c r="V150" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W150" s="6" t="inlineStr">
+        <is>
+          <t>Cinderella dress pendant from Rommanel's Disney collection, plated in 18K gold with resin detail. A sweet gift for a little girl who loves Disney princesses, to wear on a favourite chain.
+• Material: 18K gold plated, with three layers of gold
+• From the Disney Collection
+• Resin detail
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X150" s="6" t="inlineStr"/>
+      <c r="Y150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -15036,9 +17326,26 @@
       <c r="S151" s="4" t="inlineStr"/>
       <c r="T151" s="4" t="inlineStr"/>
       <c r="U151" s="4" t="inlineStr"/>
-      <c r="V151" s="4" t="inlineStr"/>
-      <c r="W151" s="6" t="inlineStr"/>
-      <c r="X151" s="7" t="inlineStr">
+      <c r="V151" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W151" s="6" t="inlineStr">
+        <is>
+          <t>Long 18K gold-plated Venetian chain necklace, 80 cm, with smooth 2.5 mm beads spaced along the chain. Wear it long on its own or layer it with shorter necklaces.
+• Material: 18K gold plated, with three layers of gold
+• Length: 80 cm
+• Venetian chain, 0.85 mm
+• Smooth 2.5 mm hollow beads spaced along the chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X151" s="6" t="inlineStr"/>
+      <c r="Y151" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -15134,13 +17441,25 @@
       <c r="U152" s="4" t="inlineStr"/>
       <c r="V152" s="4" t="inlineStr">
         <is>
-          <t>trocou '24k, 18k &amp; 22k' por 'Triple-layer gold finish'</t>
-        </is>
-      </c>
-      <c r="W152" s="6" t="inlineStr"/>
-      <c r="X152" s="7" t="inlineStr">
-        <is>
-          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a importação 2 troca por 'Triple-layer gold finish'.</t>
+          <t>descrição nova; trocou '24k, 18k &amp; 22k' por 'Triple-layer gold finish'</t>
+        </is>
+      </c>
+      <c r="W152" s="6" t="inlineStr">
+        <is>
+          <t>Heart pendant necklace in 18K gold plate, the heart pavé-set with 29 tiny white cubic zirconia, on a 50 cm chain that adjusts to 45 cm. A meaningful gift for a partner, mum or daughter.
+• Material: 18K gold plated, with three layers of gold
+• Length: 50 cm, adjustable to 45 cm
+• Stones: 29 white cubic zirconia, 1 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X152" s="6" t="inlineStr"/>
+      <c r="Y152" s="7" t="inlineStr">
+        <is>
+          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a descrição nova da importação 2 diz 'three layers of gold'.</t>
         </is>
       </c>
     </row>
@@ -15234,13 +17553,25 @@
       <c r="U153" s="4" t="inlineStr"/>
       <c r="V153" s="4" t="inlineStr">
         <is>
-          <t>trocou '24k, 18k &amp; 22k' por 'Triple-layer gold finish'</t>
-        </is>
-      </c>
-      <c r="W153" s="6" t="inlineStr"/>
-      <c r="X153" s="7" t="inlineStr">
-        <is>
-          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a importação 2 troca por 'Triple-layer gold finish'.</t>
+          <t>descrição nova; trocou '24k, 18k &amp; 22k' por 'Triple-layer gold finish'</t>
+        </is>
+      </c>
+      <c r="W153" s="6" t="inlineStr">
+        <is>
+          <t>Fine 18K gold-plated chain necklace in a 42 cm length, made of 0.3 mm faceted piastrine links. Wear it alone for a minimal look or layer it with longer chains.
+• Material: 18K gold plated, with three layers of gold
+• Length: 42 cm
+• Faceted piastrine link chain, 0.3 mm
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X153" s="6" t="inlineStr"/>
+      <c r="Y153" s="7" t="inlineStr">
+        <is>
+          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a descrição nova da importação 2 diz 'three layers of gold'.</t>
         </is>
       </c>
     </row>
@@ -15332,9 +17663,27 @@
       <c r="S154" s="4" t="inlineStr"/>
       <c r="T154" s="4" t="inlineStr"/>
       <c r="U154" s="4" t="inlineStr"/>
-      <c r="V154" s="4" t="inlineStr"/>
-      <c r="W154" s="6" t="inlineStr"/>
-      <c r="X154" s="4" t="inlineStr"/>
+      <c r="V154" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W154" s="6" t="inlineStr">
+        <is>
+          <t>Disney Cinderella slipper earrings plated in 18K gold, each little shoe finished with resin detail and a 3.5 mm cubic zirconia. A magical birthday gift for a young Cinderella fan.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.9 cm x 0.6 cm
+• Stones: Two 3.5 mm cubic zirconia, one per earring
+• From the Disney Collection
+• Resin detail
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X154" s="6" t="inlineStr"/>
+      <c r="Y154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -15424,9 +17773,25 @@
       <c r="S155" s="4" t="inlineStr"/>
       <c r="T155" s="4" t="inlineStr"/>
       <c r="U155" s="4" t="inlineStr"/>
-      <c r="V155" s="4" t="inlineStr"/>
-      <c r="W155" s="6" t="inlineStr"/>
-      <c r="X155" s="4" t="inlineStr"/>
+      <c r="V155" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W155" s="6" t="inlineStr">
+        <is>
+          <t>Oval link bracelet in 18K gold plate, mixing hollow oval links with smooth and faceted ones. Adjustable from 21 cm to 18 cm, for everyday wear or dressing up.
+• Material: 18K gold plated, with three layers of gold
+• Length: 21 cm, adjustable to 18 cm
+• Hollow oval links mixed with smooth and faceted links
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X155" s="6" t="inlineStr"/>
+      <c r="Y155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -15516,9 +17881,25 @@
       <c r="S156" s="4" t="inlineStr"/>
       <c r="T156" s="4" t="inlineStr"/>
       <c r="U156" s="4" t="inlineStr"/>
-      <c r="V156" s="4" t="inlineStr"/>
-      <c r="W156" s="6" t="inlineStr"/>
-      <c r="X156" s="7" t="inlineStr">
+      <c r="V156" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W156" s="6" t="inlineStr">
+        <is>
+          <t>Open heart bracelet in 18K gold plate, 19 cm long and formed by little open hearts, each 0.9 cm x 0.5 cm. A lovely gift for a daughter, a sister or a best friend.
+• Material: 18K gold plated, with three layers of gold
+• Length: 19 cm
+• Open hearts, 0.9 cm x 0.5 cm each
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X156" s="6" t="inlineStr"/>
+      <c r="Y156" s="7" t="inlineStr">
         <is>
           <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
@@ -15612,9 +17993,25 @@
       <c r="S157" s="4" t="inlineStr"/>
       <c r="T157" s="4" t="inlineStr"/>
       <c r="U157" s="4" t="inlineStr"/>
-      <c r="V157" s="4" t="inlineStr"/>
-      <c r="W157" s="6" t="inlineStr"/>
-      <c r="X157" s="4" t="inlineStr"/>
+      <c r="V157" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W157" s="6" t="inlineStr">
+        <is>
+          <t>Classic ball bracelet in 18K gold plate, made up of 2.5 mm balls and measuring 18 to 19 cm. A simple everyday piece to wear alone or with a watch.
+• Material: 18K gold plated, with three layers of gold
+• Length: 18 to 19 cm
+• Made up of 2.5 mm balls
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X157" s="6" t="inlineStr"/>
+      <c r="Y157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -15704,9 +18101,26 @@
       <c r="S158" s="4" t="inlineStr"/>
       <c r="T158" s="4" t="inlineStr"/>
       <c r="U158" s="4" t="inlineStr"/>
-      <c r="V158" s="4" t="inlineStr"/>
-      <c r="W158" s="6" t="inlineStr"/>
-      <c r="X158" s="4" t="inlineStr"/>
+      <c r="V158" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W158" s="6" t="inlineStr">
+        <is>
+          <t>Mother and son keepsake: a little boy pendant plated in 18K gold and set with 18 tiny cubic zirconia, 1.3 cm x 0.9 cm. Add it to mum's favourite chain for Mother's Day, a birthday or a new arrival.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.3 cm x 0.9 cm
+• Stones: 18 cubic zirconia, 1 mm
+• Chain sold separately
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X158" s="6" t="inlineStr"/>
+      <c r="Y158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -15796,13 +18210,29 @@
       <c r="S159" s="4" t="inlineStr"/>
       <c r="T159" s="4" t="inlineStr"/>
       <c r="U159" s="4" t="inlineStr"/>
-      <c r="V159" s="4" t="inlineStr"/>
+      <c r="V159" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W159" s="6" t="inlineStr">
         <is>
+          <t>Gourmet chain choker in 18K gold plate, the classic curb-style chain in a short 35 cm length. Wear it alone or layer it with longer necklaces and pendants.
+• Material: 18K gold plated, with three layers of gold
+• Length: 35 cm
+• Gourmet (curb) chain
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X159" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-gourmet-chain-choker-35-cm-53234600</t>
         </is>
       </c>
-      <c r="X159" s="4" t="inlineStr"/>
+      <c r="Y159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
@@ -15892,9 +18322,24 @@
       <c r="S160" s="4" t="inlineStr"/>
       <c r="T160" s="4" t="inlineStr"/>
       <c r="U160" s="4" t="inlineStr"/>
-      <c r="V160" s="4" t="inlineStr"/>
-      <c r="W160" s="6" t="inlineStr"/>
-      <c r="X160" s="4" t="inlineStr"/>
+      <c r="V160" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W160" s="6" t="inlineStr">
+        <is>
+          <t>Kids' gold-plated apple stud earrings, set with crystals for a little sparkle. A fun gift for a birthday or the start of a new school year.
+• Material: 18K gold plated, with three layers of gold
+• Stones: Crystals
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X160" s="6" t="inlineStr"/>
+      <c r="Y160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -15984,9 +18429,26 @@
       <c r="S161" s="4" t="inlineStr"/>
       <c r="T161" s="4" t="inlineStr"/>
       <c r="U161" s="4" t="inlineStr"/>
-      <c r="V161" s="4" t="inlineStr"/>
-      <c r="W161" s="6" t="inlineStr"/>
-      <c r="X161" s="4" t="inlineStr"/>
+      <c r="V161" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W161" s="6" t="inlineStr">
+        <is>
+          <t>Smooth two-tone hoop earrings, 1.6 cm, plated in 18K gold with rhodium plating. A neat way to mix gold and silver tones in one everyday pair.
+• Material: 18K gold plated, with three layers of gold and rhodium-plated details
+• Size: 1.6 cm
+• Smooth finish
+• Two-tone: 18K gold plating with rhodium plating
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X161" s="6" t="inlineStr"/>
+      <c r="Y161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
@@ -16076,13 +18538,28 @@
       <c r="S162" s="4" t="inlineStr"/>
       <c r="T162" s="4" t="inlineStr"/>
       <c r="U162" s="4" t="inlineStr"/>
-      <c r="V162" s="4" t="inlineStr"/>
+      <c r="V162" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
       <c r="W162" s="6" t="inlineStr">
         <is>
+          <t>Little heart hoop earrings plated in 18K gold, 1.5 cm across, with open hearts for a romantic everyday look. A sweet gift for Valentine's Day or a daughter's birthday.
+• Material: 18K gold plated, with three layers of gold
+• Size: 1.5 cm diameter
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X162" s="6" t="inlineStr">
+        <is>
           <t>18k-gold-plated-open-heart-hoop-earrings-52335100</t>
         </is>
       </c>
-      <c r="X162" s="4" t="inlineStr"/>
+      <c r="Y162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -16172,12 +18649,28 @@
       <c r="S163" s="4" t="inlineStr"/>
       <c r="T163" s="4" t="inlineStr"/>
       <c r="U163" s="4" t="inlineStr"/>
-      <c r="V163" s="4" t="inlineStr"/>
-      <c r="W163" s="6" t="inlineStr"/>
-      <c r="X163" s="4" t="inlineStr"/>
+      <c r="V163" s="4" t="inlineStr">
+        <is>
+          <t>descrição nova</t>
+        </is>
+      </c>
+      <c r="W163" s="6" t="inlineStr">
+        <is>
+          <t>Tiny gold-plated butterfly stud earrings, just 0.6 cm x 0.6 cm, with a granite-effect texture. A dainty everyday pair for anyone who loves butterflies.
+• Material: 18K gold plated, with three layers of gold
+• Size: 0.6 cm x 0.6 cm
+• Granite-effect textured finish
+• Hypoallergenic and nickel-free, designed with sensitive skin in mind
+• Water-resistant and made to last, for everyday wear
+• Authentic Rommanel, designed in Brazil
+Care: put it on after perfume and creams, and take it off for the beach, the pool and hot showers to keep the shine for longer.</t>
+        </is>
+      </c>
+      <c r="X163" s="6" t="inlineStr"/>
+      <c r="Y163" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X163"/>
+  <autoFilter ref="A1:Y163"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -17462,7 +19955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17619,7 +20112,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
+          <t>18K Gold-Plated Mini Butterfly Pendant and Earrings Set</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -17655,11 +20148,11 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Maxi Wire Ring with Sphere</t>
+          <t>18K Gold-Plated Mini Butterfly Studs with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -17669,17 +20162,17 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
+          <t>O título e a descrição para o Google de hoje falam de anel ('Butterfly Ring for Girls'), mas a peça é um par de brincos de borboleta. Corrija em Search engine listing: as importações não mexem nesses textos.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Maxi Triple Band Ring with Cubic Zirconia</t>
+          <t>18K Gold-Plated Maxi Wire Ring with Sphere</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -17689,17 +20182,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Anel sem opção de tamanho e com código curto (513639), sem o aro: veja o aro na etiqueta da peça e informe no anúncio.</t>
+          <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Hoop Earrings with Cubic Zirconia Drops</t>
+          <t>18K Gold-Plated Maxi Triple Band Ring with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -17709,17 +20202,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>Anel sem opção de tamanho e com código curto (513639), sem o aro: veja o aro na etiqueta da peça e informe no anúncio.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Skinny Infinity Ring</t>
+          <t>18K Gold-Plated Hoop Earrings with Cubic Zirconia Drops</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -17729,17 +20222,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Double Band Ring with Spheres and Cubic Zirconia</t>
+          <t>18K Gold-Plated Skinny Infinity Ring</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -17749,17 +20242,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Anel sem opção de tamanho: o código termina em ...1206, ou seja aro 12 (confira na peça). Informe o tamanho no anúncio.</t>
+          <t>Anel sem opção de tamanho: o código termina em ...1400, ou seja aro 14 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Skinny Butterfly Ring with Cubic Zirconia</t>
+          <t>18K Gold-Plated Double Band Ring with Spheres and Cubic Zirconia</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -17769,17 +20262,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Anel sem opção de tamanho: o código termina em ...1606, ou seja aro 16 (confira na peça). Informe o tamanho no anúncio.</t>
+          <t>Anel sem opção de tamanho: o código termina em ...1206, ou seja aro 12 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Personalised Bar Necklace</t>
+          <t>18K Gold-Plated Skinny Butterfly Ring with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -17789,17 +20282,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Colar personalizável: explique na descrição como a cliente envia o nome (campo de texto ou mensagem).</t>
+          <t>Anel sem opção de tamanho: o código termina em ...1606, ou seja aro 16 (confira na peça). Informe o tamanho no anúncio.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Ribbed Half Hoop Earrings, 1.3 cm</t>
+          <t>18K Gold-Plated Personalised Bar Necklace</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -17809,17 +20302,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>Colar personalizável: explique na descrição como a cliente envia o nome (campo de texto ou mensagem).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Huggie Hoop Earrings with Cubic Zirconia</t>
+          <t>18K Gold-Plated Ribbed Half Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -17835,11 +20328,11 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Salamander Chain Choker, 38 cm</t>
+          <t>18K Gold-Plated Huggie Hoop Earrings with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -17849,17 +20342,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Medical grade' sem comprovação: a importação 2 tira essa frase.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>925 Sterling Silver Teardrop Cubic Zirconia Stud Earrings</t>
+          <t>18K Gold-Plated Salamander Chain Choker, 38 cm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -17869,17 +20362,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>A descrição diz 'Medical grade' sem comprovação: a descrição nova da importação 2 não traz essa frase.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Pavé Half Hoop Earrings</t>
+          <t>925 Sterling Silver Teardrop Cubic Zirconia Stud Earrings</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -17895,11 +20388,11 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Smooth Half Hoop Earrings, 1.3 cm</t>
+          <t>18K Gold-Plated Pavé Half Hoop Earrings</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -17915,11 +20408,11 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Fine Lock Chain Necklace, 42 cm</t>
+          <t>18K Gold-Plated Smooth Half Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -17929,17 +20422,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Parece ser o mesmo colar do #21 (mesmo código-base 531638, mesma descrição). Mantenha um só e crie um redirecionamento do outro.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Black Butterfly Stud Earrings</t>
+          <t>18K Gold-Plated Fine Lock Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -17949,17 +20442,17 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>Parece ser o mesmo colar do #21 (mesmo código-base 531638, mesma descrição). Mantenha um só e crie um redirecionamento do outro.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated White Butterfly Stud Earrings</t>
+          <t>18K Gold-Plated Black Butterfly Stud Earrings</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -17975,11 +20468,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Ball Stud Earrings, 8 mm</t>
+          <t>18K Gold-Plated White Butterfly Stud Earrings</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -17995,11 +20488,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Ball Stud Earrings, 4 mm</t>
+          <t>18K Gold-Plated Ball Stud Earrings, 8 mm</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -18015,11 +20508,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Plain Hoop Earrings, 1.7 cm</t>
+          <t>18K Gold-Plated Ball Stud Earrings, 4 mm</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -18035,11 +20528,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>925 Sterling Silver Green Teardrop Stud Earrings</t>
+          <t>18K Gold-Plated Plain Hoop Earrings, 1.7 cm</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -18055,11 +20548,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>925 Sterling Silver Solitaire Ring with Cubic Zirconia</t>
+          <t>925 Sterling Silver Green Teardrop Stud Earrings</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -18069,17 +20562,17 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Anel de prata 925 com o código 510139, que é o mesmo do anel banhado a ouro (#122). Códigos de prata da Rommanel começam com 8: confira o código certo.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Heart Link Bracelet, 19 cm</t>
+          <t>925 Sterling Silver Solitaire Ring with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -18089,17 +20582,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>Anel de prata 925 com o código 510139, que é o mesmo do anel banhado a ouro (#122). Códigos de prata da Rommanel começam com 8: confira o código certo.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Y Necklace with Cubic Zirconia</t>
+          <t>18K Gold-Plated Heart Link Bracelet, 19 cm</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -18109,17 +20602,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Estava com o tipo EARRINGS, mas é um colar (Y necklace).</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Textured Hoop Earrings, 1.1 cm</t>
+          <t>18K Gold-Plated Y Necklace with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -18129,17 +20622,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>Estava com o tipo EARRINGS, mas é um colar (Y necklace).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Green Cubic Zirconia Half Hoop Earrings</t>
+          <t>18K Gold-Plated Textured Hoop Earrings, 1.1 cm</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -18155,11 +20648,11 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Black Heart Solitaire Ring</t>
+          <t>18K Gold-Plated Green Cubic Zirconia Half Hoop Earrings</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -18169,17 +20662,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Size: 16 (BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Blue Crystal Ring with Cubic Zirconia</t>
+          <t>18K Gold-Plated Black Heart Solitaire Ring</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -18189,17 +20682,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Size: 14(BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
+          <t>A descrição diz 'Size: 16 (BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Venetian Bead Chain Necklace, 80 cm</t>
+          <t>18K Gold-Plated Blue Crystal Ring with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -18209,17 +20702,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>A descrição diz 'Size: 14(BR)', mas o anúncio oferece 7 tamanhos (N a Z+1). Confira quais tamanhos você tem de verdade.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Pavé Heart Pendant Necklace, 50 cm</t>
+          <t>18K Gold-Plated Venetian Bead Chain Necklace, 80 cm</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -18229,17 +20722,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a importação 2 troca por 'Triple-layer gold finish'.</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Piastrine Chain Necklace, 42 cm</t>
+          <t>18K Gold-Plated Pavé Heart Pendant Necklace, 50 cm</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -18249,17 +20742,17 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a importação 2 troca por 'Triple-layer gold finish'.</t>
+          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a descrição nova da importação 2 diz 'three layers of gold'.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Open Heart Bracelet, 19 cm</t>
+          <t>18K Gold-Plated Piastrine Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -18269,17 +20762,17 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
+          <t>A descrição diz 'Triple gold finish (24k, 18k &amp; 22k)'. A Rommanel não publica essa divisão: a descrição nova da importação 2 diz 'three layers of gold'.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
+          <t>18K Gold-Plated Open Heart Bracelet, 19 cm</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -18289,17 +20782,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (gargantilha-banhada-a-ouro-18k-fio-grumet-5306944200). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-curb-chain-necklace-42-cm-5306944200 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O título para o Google de hoje é igual ao de outro produto: diferencie (tamanho, pedra, cor).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Solitaire Pendant Necklace, 40 cm</t>
+          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -18309,17 +20802,17 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (gargantilha-com-pingente-solitario-banhada-a-ouro-18k-53200506). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-solitaire-pendant-necklace-40-cm-53200506 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (gargantilha-banhada-a-ouro-18k-fio-grumet-5306944200). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-curb-chain-necklace-42-cm-5306944200 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Classic Hoop Earrings, 1.8 cm</t>
+          <t>18K Gold-Plated Solitaire Pendant Necklace, 40 cm</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -18329,17 +20822,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (52080700). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-classic-hoop-earrings-1-8-cm-52080700 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (gargantilha-com-pingente-solitario-banhada-a-ouro-18k-53200506). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-solitaire-pendant-necklace-40-cm-53200506 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Interlocking Circles Earrings</t>
+          <t>18K Gold-Plated Classic Hoop Earrings, 1.8 cm</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -18349,17 +20842,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (brinco-circulos-entrelacados-banhado-a-ouro-18k-52431000). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-interlocking-circles-earrings-52431000 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (52080700). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-classic-hoop-earrings-1-8-cm-52080700 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Heart Crystal Earrings</t>
+          <t>18K Gold-Plated Interlocking Circles Earrings</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -18369,17 +20862,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (brinco-coracao-banhado-a-ouro-18k-com-cristais-522372). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-heart-crystal-earrings-522372 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (brinco-circulos-entrelacados-banhado-a-ouro-18k-52431000). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-interlocking-circles-earrings-52431000 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Ball Pendant Necklace, 45 cm</t>
+          <t>18K Gold-Plated Heart Crystal Earrings</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -18389,17 +20882,17 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (gargantilha-com-pingente-esfera-banhada-a-ouro-18k-53254900). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-ball-pendant-necklace-45-cm-53254900 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (brinco-coracao-banhado-a-ouro-18k-com-cristais-522372). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-heart-crystal-earrings-522372 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Huggie Hoop Earrings with Cubic Zirconia</t>
+          <t>18K Gold-Plated Ball Pendant Necklace, 45 cm</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -18409,17 +20902,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (brinco-argola-banhado-a-ouro-18k-com-zirconias-52321406). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-huggie-hoop-earrings-with-cubic-zirconia-52321406 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (gargantilha-com-pingente-esfera-banhada-a-ouro-18k-53254900). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-ball-pendant-necklace-45-cm-53254900 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Teardrop Stud Earrings</t>
+          <t>18K Gold-Plated Huggie Hoop Earrings with Cubic Zirconia</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -18429,17 +20922,17 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-dometer-earring-52747800). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-teardrop-stud-earrings-52747800 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (brinco-argola-banhado-a-ouro-18k-com-zirconias-52321406). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-huggie-hoop-earrings-with-cubic-zirconia-52321406 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Gourmet Chain Choker, 35 cm</t>
+          <t>18K Gold-Plated Teardrop Stud Earrings</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -18449,17 +20942,17 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-groumet-chain-necklace-53234600). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-gourmet-chain-choker-35-cm-53234600 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-dometer-earring-52747800). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-teardrop-stud-earrings-52747800 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Open Heart Hoop Earrings</t>
+          <t>18K Gold-Plated Gourmet Chain Choker, 35 cm</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -18469,17 +20962,17 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-hoop-earrings-with-openheart-design-5233510000). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-open-heart-hoop-earrings-52335100 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
+          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-groumet-chain-necklace-53234600). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-gourmet-chain-choker-35-cm-53234600 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Holy Spirit Dove Earrings</t>
+          <t>18K Gold-Plated Open Heart Hoop Earrings</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -18489,17 +20982,17 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>O link do produto está em português, só com números ou com erro (18k-gold-plated-hoop-earrings-with-openheart-design-5233510000). No produto, em 'Search engine listing' (listagem nos mecanismos de pesquisa), troque o 'URL handle' para 18k-gold-plated-open-heart-hoop-earrings-52335100 e deixe marcado 'Create a URL redirect' (criar redirecionamento).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Triple Hoop Earrings</t>
+          <t>18K Gold-Plated Holy Spirit Dove Earrings</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -18509,17 +21002,17 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Four-Leaf Clover Earrings</t>
+          <t>18K Gold-Plated Triple Hoop Earrings</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -18529,17 +21022,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Hoop Earrings with Pear Cubic Zirconia Drops</t>
+          <t>18K Gold-Plated Four-Leaf Clover Earrings</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -18549,17 +21042,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Flower Stud Earring Set</t>
+          <t>18K Gold-Plated Hoop Earrings with Pear Cubic Zirconia Drops</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -18569,17 +21062,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Mini Butterfly Necklace and Earrings Set</t>
+          <t>18K Gold-Plated Flower Stud Earring Set</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -18589,17 +21082,17 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Bezel Crystal Stud Earrings, 4 mm</t>
+          <t>18K Gold-Plated Mini Butterfly Pendant and Earrings Set</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -18609,17 +21102,17 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Cable Chain Necklace, 50 cm</t>
+          <t>18K Gold-Plated Bezel Crystal Stud Earrings, 4 mm</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -18629,17 +21122,17 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Cable Chain Necklace, 45 cm</t>
+          <t>18K Gold-Plated Cable Chain Necklace, 50 cm</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -18649,17 +21142,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
+          <t>18K Gold-Plated Cable Chain Necklace, 45 cm</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -18669,17 +21162,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Crystal Solitaire Stud Earrings</t>
+          <t>18K Gold-Plated Curb Chain Necklace, 42 cm</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -18689,17 +21182,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Children's 18K Gold-Plated Ball Drop Earrings</t>
+          <t>18K Gold-Plated Crystal Solitaire Stud Earrings</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -18709,17 +21202,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Textured Hoop Earrings, 1.3 cm</t>
+          <t>Children's 18K Gold-Plated Ball Drop Earrings</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -18729,17 +21222,17 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Children's 18K Gold-Plated Bow Stud Earrings</t>
+          <t>18K Gold-Plated Textured Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -18749,17 +21242,17 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Wide Huggie Hoop Earrings, 1.3 cm</t>
+          <t>Children's 18K Gold-Plated Bow Stud Earrings</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -18769,17 +21262,17 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Crystal Ear Climber Earrings</t>
+          <t>18K Gold-Plated Wide Huggie Hoop Earrings, 1.3 cm</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -18789,17 +21282,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>18K Gold-Plated Oval Hoop Earrings, 1.8 cm</t>
+          <t>18K Gold-Plated Crystal Ear Climber Earrings</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -18809,45 +21302,47 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>18K Gold-Plated Oval Hoop Earrings, 1.8 cm</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>18K Gold-Plated Lock Chain Necklace, 42 cm</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>A descrição diz 'Waterproof' (à prova d'água). A importação 2 troca por 'Water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Todas as fotos</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Nenhuma das 436 fotos tem texto alternativo. O tema novo usa o título limpo como texto alternativo enquanto você não escreve um, mas o ideal é descrever cada foto (ex.: 'brinco de borboleta na orelha da modelo').</t>
+          <t>A descrição de hoje diz 'Waterproof' (à prova d'água). A descrição nova da importação 2 diz 'water-resistant', que diz que pode molhar sem prometer que aguenta mar e piscina.</t>
         </is>
       </c>
     </row>
@@ -18859,13 +21354,13 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Tipos de produto</t>
+          <t>Todas as fotos</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Hoje há 9 grafias diferentes para as mesmas coisas (EARRINGS, EARRING, Brinco, CHEKER...) e 33 produtos sem tipo. A importação 1 deixa só 7: Earrings, Necklaces, Pendants, Rings, Bracelets, Anklets, Jewellery Sets.</t>
+          <t>Nenhuma das 436 fotos tem texto alternativo. O tema novo usa o título limpo como texto alternativo enquanto você não escreve um, mas o ideal é descrever cada foto (ex.: 'brinco de borboleta na orelha da modelo').</t>
         </is>
       </c>
     </row>
@@ -18877,13 +21372,13 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Coleções incompletas</t>
+          <t>Tipos de produto</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>63 produtos não estão na coleção da categoria deles (ex.: 25 brincos fora de 'Earrings'). Com os tipos padronizados, dá para transformar as coleções em automáticas (veja o guia).</t>
+          <t>Hoje há 9 grafias diferentes para as mesmas coisas (EARRINGS, EARRING, Brinco, CHEKER...) e 33 produtos sem tipo. A importação 1 deixa só 7: Earrings, Necklaces, Pendants, Rings, Bracelets, Anklets, Jewellery Sets.</t>
         </is>
       </c>
     </row>
@@ -18895,17 +21390,13 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Coleção 18K Gold Plated</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
+          <t>Coleções incompletas</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
+          <t>63 produtos não estão na coleção da categoria deles (ex.: 25 brincos fora de 'Earrings'). Com os tipos padronizados, dá para transformar as coleções em automáticas (veja o guia).</t>
         </is>
       </c>
     </row>
@@ -18917,7 +21408,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Coleção All Jewellery</t>
+          <t>Coleção 18K Gold Plated</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -18927,7 +21418,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>O texto diz 'waterproof' (troque por 'water-resistant'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
+          <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
@@ -18939,7 +21430,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Coleção EOFY Gold</t>
+          <t>Coleção All Jewellery</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -18961,22 +21452,44 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
+          <t>Coleção EOFY Gold</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>O texto diz 'waterproof' (troque por 'water-resistant'). Corrija em Produtos › Coleções, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>Página About us</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>abrir</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>abrir</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>O texto diz '24k, 18k e 22k' (a Rommanel só diz 'três camadas de ouro'). Corrija em Loja virtual › Páginas, no campo Descrição/Conteúdo; a importação não mexe nisso.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D75"/>
+  <autoFilter ref="A1:D76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -19045,10 +21558,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
